--- a/data.xlsx
+++ b/data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,32 +447,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lng</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>city</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>lng</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>image</t>
         </is>
       </c>
     </row>
@@ -482,36 +482,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Đại Nội Huế</t>
+          <t>Hoàng Thành Huế</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hoàng thành cổ kính.</t>
+          <t>Hoàng thành cổ kính, di sản UNESCO với cung điện và thành lũy Nguyễn triều.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Di tích</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>4.9</v>
+      </c>
       <c r="F2" t="n">
-        <v>4.9</v>
+        <v>16.47005</v>
       </c>
       <c r="G2" t="n">
-        <v>16.4689</v>
-      </c>
-      <c r="H2" t="n">
-        <v>107.5779</v>
+        <v>107.57738</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>/static/images/dai-noi-hue.png</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>/static/images/dai-noi-hue.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -521,36 +521,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chùa Thiên Mụ</t>
+          <t>Cung An Định</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chùa cổ bên sông Hương.</t>
+          <t>Biệt thự cổ kiến trúc Châu Âu độc đáo, nơi ở của gia đình vua Bảo Đại.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Tâm linh</t>
-        </is>
+          <t>Di tích</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4.7</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8</v>
+        <v>16.45659</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4534</v>
-      </c>
-      <c r="H3" t="n">
-        <v>107.5449</v>
+        <v>107.59832</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>/static/images/cung-an-dinh.png</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>/static/images/chua-thien-mu.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -560,36 +560,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chợ Đông Ba</t>
+          <t>Đàn Nam Giao</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Khu chợ sầm uất.</t>
+          <t>Nơi các vua Nguyễn tế trời đất, không gian trang nghiêm cổ kính.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Mua sắm</t>
-        </is>
+          <t>Di tích</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>16.4378</v>
       </c>
       <c r="G4" t="n">
-        <v>16.4703</v>
-      </c>
-      <c r="H4" t="n">
-        <v>107.581</v>
+        <v>107.5827</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>/static/images/dan-nam-giao.png</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>/static/images/cho-dong-ba.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -599,36 +599,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lăng Khải Định</t>
+          <t>Chùa Thiên Mụ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kiến trúc lăng tẩm độc đáo.</t>
+          <t>Ngôi chùa cổ nhất Huế bên sông Hương, tháp Phước Duyên biểu tượng.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Di tích</t>
-        </is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7</v>
+        <v>16.4537</v>
       </c>
       <c r="G5" t="n">
-        <v>16.3993</v>
-      </c>
-      <c r="H5" t="n">
-        <v>107.5903</v>
+        <v>107.54458</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>/static/images/chua-thien-mu.png</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>/static/images/lang-khai-dinh.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -638,36 +638,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cầu Tràng Tiền</t>
+          <t>Chùa Từ Đàm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cây cầu biểu tượng.</t>
+          <t>Trung tâm Phật giáo Huế, nơi khởi xướng phong trào 1963.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Tham quan</t>
-        </is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4.6</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8</v>
+        <v>16.45153</v>
       </c>
       <c r="G6" t="n">
-        <v>16.4685</v>
-      </c>
-      <c r="H6" t="n">
-        <v>107.5923</v>
+        <v>107.58178</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>/static/images/chua-tu-dam.png</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>/static/images/cau-trang-tien.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -677,36 +677,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bún Bò Mệ Kéo</t>
+          <t>Chùa Báo Quốc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bún bò đậm đà.</t>
+          <t>Chùa cổ trên đồi, xây năm 1670, vườn thông yên tĩnh học Phật.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ẩm thực</t>
-        </is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4.7</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>16.45421</v>
       </c>
       <c r="G7" t="n">
-        <v>16.4732</v>
-      </c>
-      <c r="H7" t="n">
-        <v>107.5955</v>
+        <v>107.57962</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>/static/images/chua-bao-quoc.png</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>/static/images/bunbo.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -716,36 +716,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chè Hẻm</t>
+          <t>Chùa Từ Hiếu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quán chè nổi tiếng.</t>
+          <t>Chùa tổ của Thiền sư Thích Nhất Hạnh, vườn mộ giữa rừng thông.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Ẩm thực</t>
-        </is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4.8</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>16.43889</v>
       </c>
       <c r="G8" t="n">
-        <v>16.471</v>
-      </c>
-      <c r="H8" t="n">
-        <v>107.593</v>
+        <v>107.57199</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>/static/images/chua-tu-hieu.png</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>/static/images/chehem.png</t>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -755,36 +755,1167 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Chùa Huyền Không Sơn Thượng</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chùa trên núi, hồ sen, thư pháp, kiến trúc hòa quyện thiên nhiên.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.45078</v>
+      </c>
+      <c r="G9" t="n">
+        <v>107.49381</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>/static/images/chua-huyen-khong-son-thuong.png</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chùa Thiền Lâm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kiến trúc kiểu Ấn Độ với tượng Phật trắng lớn.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16.43817</v>
+      </c>
+      <c r="G10" t="n">
+        <v>107.57528</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>/static/images/chua-thien-lam.png</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Điện Hòn Chén</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ngôi điện linh thiêng nằm bên bờ sông Hương.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16.42195</v>
+      </c>
+      <c r="G11" t="n">
+        <v>107.56296</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>/static/images/dien-hon-chen.png</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lăng Khải Định</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lăng tẩm độc đáo kết hợp kiến trúc Á-Âu.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.3989</v>
+      </c>
+      <c r="G12" t="n">
+        <v>107.59029</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>/static/images/lang-khai-dinh.png</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lăng Tự Đức</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lăng mộ lãng mạn nhất của vua Tự Đức, hồ sen và kiến trúc thơ mộng.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16.43299</v>
+      </c>
+      <c r="G13" t="n">
+        <v>107.56644</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>/static/images/lang-tu-duc.png</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lăng Minh Mạng</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lăng mộ hoành tráng nhất, kiến trúc đối xứng hoàn hảo bên sông Hương.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.38748</v>
+      </c>
+      <c r="G14" t="n">
+        <v>107.57025</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>/static/images/lang-minh-mang.png</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lăng Gia Long</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lăng mộ xa xôi nhất, nằm giữa núi rừng thiên nhiên hùng vĩ.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16.36197</v>
+      </c>
+      <c r="G15" t="n">
+        <v>107.59694</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>/static/images/lang-gia-long.png</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bún Bò Mệ Kéo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Quán bún bò Huế nguyên bản nhất, nước dùng đậm đà gia truyền.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>16.47505</v>
+      </c>
+      <c r="G16" t="n">
+        <v>107.5887</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>/static/images/bun-bo-me-keo.png</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Chè Hẻm Huế</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quán chè hẻm nổi tiếng với hơn 20 loại chè Huế truyền thống.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16.4651</v>
+      </c>
+      <c r="G17" t="n">
+        <v>107.59358</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>/static/images/che-hem-hue.png</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nem Lủi Bà Tý</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Quán nem lủi nướng nổi tiếng, ăn kèm bánh tráng và rau sống.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>16.48003</v>
+      </c>
+      <c r="G18" t="n">
+        <v>107.58339</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/static/images/nem-lui-ba-ty.png</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Chợ Đông Ba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chợ truyền thống sầm uất nhất Huế, bán đặc sản và quà lưu niệm.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mua sắm</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16.47243</v>
+      </c>
+      <c r="G19" t="n">
+        <v>107.58867</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>/static/images/cho-dong-ba.png</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chợ Bến Ngự</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chợ địa phương gần Đại Nội, bán hải sản tươi, rau củ và đặc sản Huế.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mua sắm</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16.45518</v>
+      </c>
+      <c r="G20" t="n">
+        <v>107.58394</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>/static/images/cho-ben-ngu.png</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chợ An Cựu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chợ nổi tiếng ẩm thực đường phố, gần trung tâm.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mua sắm</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>16.45745</v>
+      </c>
+      <c r="G21" t="n">
+        <v>107.6007</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/static/images/cho-an-cuu.png</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Chợ Tây Lộc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chợ dân sinh lớn, nổi tiếng mắm tôm chua và đặc sản Huế.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mua sắm</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>16.47678</v>
+      </c>
+      <c r="G22" t="n">
+        <v>107.56569</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/static/images/cho-tay-loc.png</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Chợ Xép</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chợ nhỏ truyền thống, bán trái cây, đồ cúng và không khí địa phương.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mua sắm</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>16.47888</v>
+      </c>
+      <c r="G23" t="n">
+        <v>107.58242</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/static/images/cho-xep.png</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nhà vườn An Hiên</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nhà vườn truyền thống Huế đẹp nhất, kiến trúc cổ.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nhà vườn</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.45532</v>
+      </c>
+      <c r="G24" t="n">
+        <v>107.55378</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/static/images/nha-vuon-an-hien.png</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cầu Trường Tiền</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Cây cầu biểu tượng bắc qua sông Hương, đẹp lung linh về đêm.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>16.46912</v>
+      </c>
+      <c r="G25" t="n">
+        <v>107.58859</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/static/images/cau-truong-tien.png</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sông Hương</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dòng sông thơ mộng của Huế, du thuyền nghe ca Huế về đêm.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16.47021</v>
+      </c>
+      <c r="G26" t="n">
+        <v>107.59024</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/static/images/song-huong.png</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cầu ngói Thanh Toàn</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cầu ngói cổ kính hơn 200 năm, kiến trúc Nhật Bản độc đáo.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>16.46674</v>
+      </c>
+      <c r="G27" t="n">
+        <v>107.6421</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/static/images/cau-thanh-toan.png</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Làng Hương Thủy Xuân</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Làng nghề làm hương truyền thống rực rỡ sắc màu.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>16.43554</v>
+      </c>
+      <c r="G28" t="n">
+        <v>107.56227</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/static/images/lang-huong.png</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Trường THPT chuyên Quốc Học Huế</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ngôi trường cổ kính màu đỏ gạch bên sông Hương, kiến trúc Pháp.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16.46008</v>
+      </c>
+      <c r="G29" t="n">
+        <v>107.58335</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>/static/images/truong-quoc-hoc-hue.png</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Đồi Vọng Cảnh</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ngắm hoàng hôn đẹp nhất.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Huế</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Đồi cao ngắm toàn cảnh Huế và sông Hương lúc hoàng hôn.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Thiên nhiên</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="E30" t="n">
         <v>4.7</v>
       </c>
-      <c r="G9" t="n">
-        <v>16.435</v>
-      </c>
-      <c r="H9" t="n">
-        <v>107.563</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>/static/images/doi-vong-canh-hue.png</t>
+      <c r="F30" t="n">
+        <v>16.42723</v>
+      </c>
+      <c r="G30" t="n">
+        <v>107.56493</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>/static/images/doi-vong-canh.png</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Núi Ngự Bình</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ngọn núi bình phong trấn giữ Huế.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16.44168</v>
+      </c>
+      <c r="G31" t="n">
+        <v>107.5961</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>/static/images/nui-ngu-binh.png</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Đầm Lập An</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tuyệt tình cốc của Huế, vẻ đẹp mơ màng giữa đầm nước và núi Bạch Mã.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>16.22142</v>
+      </c>
+      <c r="G32" t="n">
+        <v>108.06157</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>/static/images/dam-lap-an.png</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vườn Quốc gia Bạch Mã</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Thiên đường trên mặt đất với khí hậu mát mẻ.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16.2165</v>
+      </c>
+      <c r="G33" t="n">
+        <v>107.89365</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>/static/images/vuon-quoc-gia-bach-ma.png</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rừng ngập mặn Rú Chá</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Khu rừng ngập mặn nguyên sinh duy nhất còn lại ở phá Tam Giang.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>16.55748</v>
+      </c>
+      <c r="G34" t="n">
+        <v>107.61144</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>/static/images/rung-ru-cha.png</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Phá Tam Giang</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Vùng đầm phá nước lợ lớn nhất Đông Nam Á, nơi ngắm hoàng hôn đẹp nhất.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>16.59788</v>
+      </c>
+      <c r="G35" t="n">
+        <v>107.54309</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>/static/images/pha-tam-giang.png</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Suối Voi</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dòng suối mát lạnh với tảng đá hình con voi độc đáo.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>16.24387</v>
+      </c>
+      <c r="G36" t="n">
+        <v>107.98943</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>/static/images/suoi-voi.png</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bãi biển Lăng Cô</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Một trong những bãi biển đẹp nhất Việt Nam, vịnh Lăng Cô yên bình.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bãi biển</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F37" t="n">
+        <v>16.26424</v>
+      </c>
+      <c r="G37" t="n">
+        <v>108.06582</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>/static/images/bai-bien-lang-co.png</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bãi biển Thuận An</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bãi biển gần trung tâm Huế, hải sản tươi và không khí địa phương.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bãi biển</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16.55966</v>
+      </c>
+      <c r="G38" t="n">
+        <v>107.65428</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/static/images/bai-bien-thuan-an.png</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Huế</t>
         </is>
       </c>
     </row>
@@ -799,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,7 +1962,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +1972,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -851,7 +1982,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -861,7 +1992,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HoiYeuThienNhien</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>YeuTamLinh</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>YeuTamLinh</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -538,10 +538,10 @@
         <v>4.7</v>
       </c>
       <c r="F3" t="n">
-        <v>16.45659</v>
+        <v>16.45722</v>
       </c>
       <c r="G3" t="n">
-        <v>107.59832</v>
+        <v>107.59802</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/data.xlsx
+++ b/data.xlsx
@@ -499,10 +499,10 @@
         <v>4.9</v>
       </c>
       <c r="F2" t="n">
-        <v>16.47005</v>
+        <v>16.46883</v>
       </c>
       <c r="G2" t="n">
-        <v>107.57738</v>
+        <v>107.57815</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nem Lủi Bà Tý</t>
+          <t>Nem Lụi Bà Tý</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nhà vườn</t>
+          <t>Tham quan</t>
         </is>
       </c>
       <c r="E24" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>/static/images/dai-noi-hue.png</t>
+          <t>/static/images/hoang-thanh-hue.png</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1574,31 +1574,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Đồi Vọng Cảnh</t>
+          <t>Ga Huế</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Đồi cao ngắm toàn cảnh Huế và sông Hương lúc hoàng hôn.</t>
+          <t>Nhà ga cổ kính xây dựng từ thời Pháp thuộc, điểm check-in hoài cổ và là đầu mối giao thông quan trọng.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
+          <t>Tham quan</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F30" t="n">
-        <v>16.42723</v>
+        <v>16.45648</v>
       </c>
       <c r="G30" t="n">
-        <v>107.56493</v>
+        <v>107.57805</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>/static/images/doi-vong-canh.png</t>
+          <t>/static/images/ga-hue.png</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1613,31 +1613,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Núi Ngự Bình</t>
+          <t>Cầu Gỗ Lim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ngọn núi bình phong trấn giữ Huế.</t>
+          <t>Tuyến đường đi bộ lát gỗ lim bên bờ sông Hương, điểm ngắm hoàng hôn và check-in cực hot.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
+          <t>Tham quan</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F31" t="n">
-        <v>16.44168</v>
+        <v>16.46561</v>
       </c>
       <c r="G31" t="n">
-        <v>107.5961</v>
+        <v>107.58744</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>/static/images/nui-ngu-binh.png</t>
+          <t>/static/images/cau-go-lim.png</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Đầm Lập An</t>
+          <t>Đồi Vọng Cảnh</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuyệt tình cốc của Huế, vẻ đẹp mơ màng giữa đầm nước và núi Bạch Mã.</t>
+          <t>Đồi cao ngắm toàn cảnh Huế và sông Hương lúc hoàng hôn.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1669,14 +1669,14 @@
         <v>4.7</v>
       </c>
       <c r="F32" t="n">
-        <v>16.22142</v>
+        <v>16.42723</v>
       </c>
       <c r="G32" t="n">
-        <v>108.06157</v>
+        <v>107.56493</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>/static/images/dam-lap-an.png</t>
+          <t>/static/images/doi-vong-canh.png</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vườn Quốc gia Bạch Mã</t>
+          <t>Núi Ngự Bình</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thiên đường trên mặt đất với khí hậu mát mẻ.</t>
+          <t>Ngọn núi bình phong trấn giữ Huế.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1705,17 +1705,17 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F33" t="n">
-        <v>16.2165</v>
+        <v>16.44168</v>
       </c>
       <c r="G33" t="n">
-        <v>107.89365</v>
+        <v>107.5961</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>/static/images/vuon-quoc-gia-bach-ma.png</t>
+          <t>/static/images/nui-ngu-binh.png</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rừng ngập mặn Rú Chá</t>
+          <t>Đầm Lập An</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Khu rừng ngập mặn nguyên sinh duy nhất còn lại ở phá Tam Giang.</t>
+          <t>Tuyệt tình cốc của Huế, vẻ đẹp mơ màng giữa đầm nước và núi Bạch Mã.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1744,17 +1744,17 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F34" t="n">
-        <v>16.55748</v>
+        <v>16.22142</v>
       </c>
       <c r="G34" t="n">
-        <v>107.61144</v>
+        <v>108.06157</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>/static/images/rung-ru-cha.png</t>
+          <t>/static/images/dam-lap-an.png</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Phá Tam Giang</t>
+          <t>Vườn Quốc gia Bạch Mã</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vùng đầm phá nước lợ lớn nhất Đông Nam Á, nơi ngắm hoàng hôn đẹp nhất.</t>
+          <t>Thiên đường trên mặt đất với khí hậu mát mẻ.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1783,17 +1783,17 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F35" t="n">
-        <v>16.59788</v>
+        <v>16.2165</v>
       </c>
       <c r="G35" t="n">
-        <v>107.54309</v>
+        <v>107.89365</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>/static/images/pha-tam-giang.png</t>
+          <t>/static/images/vuon-quoc-gia-bach-ma.png</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suối Voi</t>
+          <t>Rừng ngập mặn Rú Chá</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dòng suối mát lạnh với tảng đá hình con voi độc đáo.</t>
+          <t>Khu rừng ngập mặn nguyên sinh duy nhất còn lại ở phá Tam Giang.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1822,17 +1822,17 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F36" t="n">
-        <v>16.24387</v>
+        <v>16.55748</v>
       </c>
       <c r="G36" t="n">
-        <v>107.98943</v>
+        <v>107.61144</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>/static/images/suoi-voi.png</t>
+          <t>/static/images/rung-ru-cha.png</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1847,31 +1847,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bãi biển Lăng Cô</t>
+          <t>Phá Tam Giang</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Một trong những bãi biển đẹp nhất Việt Nam, vịnh Lăng Cô yên bình.</t>
+          <t>Vùng đầm phá nước lợ lớn nhất Đông Nam Á, nơi ngắm hoàng hôn đẹp nhất.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bãi biển</t>
+          <t>Thiên nhiên</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F37" t="n">
-        <v>16.26424</v>
+        <v>16.59788</v>
       </c>
       <c r="G37" t="n">
-        <v>108.06582</v>
+        <v>107.54309</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>/static/images/bai-bien-lang-co.png</t>
+          <t>/static/images/pha-tam-giang.png</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1886,34 +1886,112 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Suối Voi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dòng suối mát lạnh với tảng đá hình con voi độc đáo.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16.24387</v>
+      </c>
+      <c r="G38" t="n">
+        <v>107.98943</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/static/images/suoi-voi.png</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Bãi biển Lăng Cô</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Một trong những bãi biển đẹp nhất Việt Nam, vịnh Lăng Cô yên bình.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bãi biển</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16.26424</v>
+      </c>
+      <c r="G39" t="n">
+        <v>108.06582</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>/static/images/bai-bien-lang-co.png</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Bãi biển Thuận An</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Bãi biển gần trung tâm Huế, hải sản tươi và không khí địa phương.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Bãi biển</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E40" t="n">
         <v>4.6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F40" t="n">
         <v>16.55966</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G40" t="n">
         <v>107.65428</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>/static/images/bai-bien-thuan-an.png</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Huế</t>
         </is>
@@ -1930,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1962,13 +2040,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KhachTayBalo</t>
+          <t>SinhVienHue</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1978,51 +2056,161 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KhachTayBalo</t>
+          <t>SinhVienHue</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HoiYeuThienNhien</t>
+          <t>KhachTayBalo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HoiYeuThienNhien</t>
+          <t>KhachTayBalo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YeuTamLinh</t>
+          <t>KhachTayBalo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>KhachTayBalo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HoiYeuThienNhien</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HoiYeuThienNhien</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HoiYeuThienNhien</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>YeuTamLinh</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>YeuTamLinh</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>YeuTamLinh</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>YeuTamLinh</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HuongDanVien</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HuongDanVien</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HuongDanVien</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HuongDanVien</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2008,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,11 +2136,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>YeuTamLinh</t>
+          <t>HoiYeuThienNhien</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -2170,17 +2170,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HuongDanVien</t>
+          <t>YeuTamLinh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2210,6 +2210,16 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HuongDanVien</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>24</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Khóa luận\Khoa_luan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0D8258-1996-46A6-B1DC-B24F51246087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F00694-8A12-4C12-8E15-FEF2A7FD958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="332">
   <si>
     <t>id</t>
   </si>
@@ -330,12 +330,6 @@
     <t>/static/images/tu-cam-thanh.png</t>
   </si>
   <si>
-    <t>Văn Miếu Huế</t>
-  </si>
-  <si>
-    <t>/static/images/van-mieu-hue.png</t>
-  </si>
-  <si>
     <t>Tượng đài Quan Thế Âm Bồ Tát</t>
   </si>
   <si>
@@ -447,12 +441,6 @@
     <t>/static/images/an-xa-tac.png</t>
   </si>
   <si>
-    <t>Bia Tiên động phương tung</t>
-  </si>
-  <si>
-    <t>/static/images/bia-tien-ong-phuong-tung.png</t>
-  </si>
-  <si>
     <t>Hồ Sơn Thọ</t>
   </si>
   <si>
@@ -507,12 +495,6 @@
     <t>/static/images/cong-vien-ho-thuy-tien.png</t>
   </si>
   <si>
-    <t>Di tích xe ô tô Thích Quảng Đức</t>
-  </si>
-  <si>
-    <t>/static/images/di-tich-xe-o-to-thich-quang-uc.png</t>
-  </si>
-  <si>
     <t>Quan Tượng Đài (Nam Đài)</t>
   </si>
   <si>
@@ -642,9 +624,6 @@
     <t>Điện Thái Hòa</t>
   </si>
   <si>
-    <t>/static/images/ien-thai-hoa.png</t>
-  </si>
-  <si>
     <t>Tây Khuyết Đài</t>
   </si>
   <si>
@@ -867,9 +846,6 @@
     <t>Tử Cấm Thành là cung điện cổ kính, biểu tượng quyền lực triều đại Minh - Thanh, nổi bật với kiến trúc nguy nga giữa lòng Bắc Kinh.</t>
   </si>
   <si>
-    <t>Văn Miếu Huế là di tích lịch sử nổi bật, lưu giữ giá trị văn hóa và truyền thống hiếu học của vùng đất cố đô.</t>
-  </si>
-  <si>
     <t>Tượng đài Quan Thế Âm Bồ Tát uy nghi giữa thiên nhiên, là điểm đến tâm linh nổi bật thu hút du khách thập phương.</t>
   </si>
   <si>
@@ -924,9 +900,6 @@
     <t>Đàn Xã Tắc là di tích lịch sử linh thiêng, nơi triều đình xưa tế lễ cầu cho quốc thái dân an tại Huế.</t>
   </si>
   <si>
-    <t>Bia Tiên động phương tung là điểm đến kỳ bí, hòa quyện giữa thiên nhiên hùng vĩ và dấu ấn lịch sử độc đáo.</t>
-  </si>
-  <si>
     <t>Hồ Sơn Thọ là điểm đến lý tưởng với cảnh sắc hữu tình, không khí trong lành, thích hợp dã ngoại và thư giãn cuối tuần.</t>
   </si>
   <si>
@@ -954,9 +927,6 @@
     <t>Công viên Hồ Thủy Tiên là điểm check-in huyền bí với hồ nước, rừng cây và rồng khổng lồ bỏ hoang giữa lòng Huế.</t>
   </si>
   <si>
-    <t>Di tích xe ô tô Thích Quảng Đức lưu giữ chiếc xe lịch sử gắn liền sự kiện tự thiêu vì hòa bình, thu hút nhiều du khách tham quan.</t>
-  </si>
-  <si>
     <t>Quan Tượng Đài (Nam Đài) là điểm ngắm cảnh lý tưởng, nơi du khách chiêm ngưỡng toàn cảnh thành phố Huế và sông Hương thơ mộng.</t>
   </si>
   <si>
@@ -1051,6 +1021,18 @@
   </si>
   <si>
     <t>Hồ Nội Kim Thủy xanh biếc, yên bình giữa núi non, là điểm đến lý tưởng để thư giãn và tận hưởng không khí trong lành.</t>
+  </si>
+  <si>
+    <t>Văn Thánh Huế</t>
+  </si>
+  <si>
+    <t>/static/images/dien-thai-hoa.png</t>
+  </si>
+  <si>
+    <t>Văn Thánh Huế là di tích lịch sử nổi bật, lưu giữ giá trị văn hóa và truyền thống hiếu học của vùng đất cố đô.</t>
+  </si>
+  <si>
+    <t>/static/images/van-thanh-hue.png</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1161,6 +1143,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H998"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.375" customWidth="1"/>
@@ -1418,14 +1401,14 @@
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A103" si="0">ROW()-ROW($A$2)+1</f>
+        <f t="shared" ref="A2:A101" si="0">ROW()-ROW($A$2)+1</f>
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -1452,7 +1435,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -1479,7 +1462,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -1506,7 +1489,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -1533,7 +1516,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
@@ -1560,7 +1543,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
@@ -1587,7 +1570,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>17</v>
@@ -1614,7 +1597,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>17</v>
@@ -1641,7 +1624,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -1668,7 +1651,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -1695,7 +1678,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>32</v>
@@ -1722,7 +1705,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -1749,7 +1732,7 @@
         <v>36</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>32</v>
@@ -1776,7 +1759,7 @@
         <v>38</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>32</v>
@@ -1803,7 +1786,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>41</v>
@@ -1830,7 +1813,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>41</v>
@@ -1857,7 +1840,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>41</v>
@@ -1884,7 +1867,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>48</v>
@@ -1911,7 +1894,7 @@
         <v>50</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>48</v>
@@ -1938,7 +1921,7 @@
         <v>52</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>48</v>
@@ -1965,7 +1948,7 @@
         <v>54</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>48</v>
@@ -1992,7 +1975,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>48</v>
@@ -2019,7 +2002,7 @@
         <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>59</v>
@@ -2046,7 +2029,7 @@
         <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>59</v>
@@ -2073,7 +2056,7 @@
         <v>63</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>59</v>
@@ -2100,7 +2083,7 @@
         <v>65</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>59</v>
@@ -2127,7 +2110,7 @@
         <v>67</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>59</v>
@@ -2154,7 +2137,7 @@
         <v>69</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>59</v>
@@ -2181,7 +2164,7 @@
         <v>71</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>59</v>
@@ -2208,7 +2191,7 @@
         <v>73</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>59</v>
@@ -2235,7 +2218,7 @@
         <v>75</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>76</v>
@@ -2262,7 +2245,7 @@
         <v>78</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>76</v>
@@ -2289,7 +2272,7 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>76</v>
@@ -2316,7 +2299,7 @@
         <v>82</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>76</v>
@@ -2343,7 +2326,7 @@
         <v>84</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>76</v>
@@ -2370,7 +2353,7 @@
         <v>86</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>76</v>
@@ -2397,7 +2380,7 @@
         <v>88</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>76</v>
@@ -2424,7 +2407,7 @@
         <v>90</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>91</v>
@@ -2451,7 +2434,7 @@
         <v>93</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>91</v>
@@ -2478,7 +2461,7 @@
         <v>95</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>59</v>
@@ -2502,10 +2485,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>97</v>
+        <v>328</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
@@ -2516,8 +2499,8 @@
       <c r="F42" s="2">
         <v>107.53890199999999</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>98</v>
+      <c r="G42" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>11</v>
@@ -2529,10 +2512,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>59</v>
@@ -2544,7 +2527,7 @@
         <v>107.5841879</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>11</v>
@@ -2556,13 +2539,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E44" s="2">
         <v>16.457834600000002</v>
@@ -2571,7 +2554,7 @@
         <v>107.5842155</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>11</v>
@@ -2583,10 +2566,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>9</v>
@@ -2598,7 +2581,7 @@
         <v>107.5898061</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>11</v>
@@ -2610,10 +2593,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>59</v>
@@ -2625,7 +2608,7 @@
         <v>107.59127290000001</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>11</v>
@@ -2637,10 +2620,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
@@ -2652,7 +2635,7 @@
         <v>107.5887</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>11</v>
@@ -2664,10 +2647,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>59</v>
@@ -2679,7 +2662,7 @@
         <v>107.5812344</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>11</v>
@@ -2691,10 +2674,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>59</v>
@@ -2706,7 +2689,7 @@
         <v>107.5758125</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>11</v>
@@ -2718,10 +2701,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>59</v>
@@ -2733,7 +2716,7 @@
         <v>107.5666428</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>11</v>
@@ -2745,10 +2728,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>59</v>
@@ -2760,7 +2743,7 @@
         <v>107.5924182</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>11</v>
@@ -2772,10 +2755,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>59</v>
@@ -2787,7 +2770,7 @@
         <v>107.5885002</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>11</v>
@@ -2799,10 +2782,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>59</v>
@@ -2814,7 +2797,7 @@
         <v>107.5997497</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>11</v>
@@ -2826,10 +2809,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>59</v>
@@ -2841,7 +2824,7 @@
         <v>107.6040878</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>11</v>
@@ -2853,10 +2836,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>59</v>
@@ -2868,7 +2851,7 @@
         <v>107.6078971</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>11</v>
@@ -2880,10 +2863,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>59</v>
@@ -2895,7 +2878,7 @@
         <v>107.65366779999999</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>11</v>
@@ -2907,10 +2890,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
@@ -2922,7 +2905,7 @@
         <v>107.5094706</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>11</v>
@@ -2934,10 +2917,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
@@ -2949,7 +2932,7 @@
         <v>107.5780681</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>11</v>
@@ -2961,10 +2944,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>9</v>
@@ -2976,7 +2959,7 @@
         <v>107.5914458</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>11</v>
@@ -2988,10 +2971,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>9</v>
@@ -3003,7 +2986,7 @@
         <v>107.5712089</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>11</v>
@@ -3015,22 +2998,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E61" s="2">
-        <v>16.471778</v>
+        <v>16.351575700000001</v>
       </c>
       <c r="F61" s="2">
-        <v>107.5782705</v>
+        <v>107.5882024</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>11</v>
@@ -3042,22 +3025,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E62" s="2">
-        <v>16.351575700000001</v>
+        <v>16.539455100000001</v>
       </c>
       <c r="F62" s="2">
-        <v>107.5882024</v>
+        <v>107.4709349</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>11</v>
@@ -3069,22 +3052,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E63" s="2">
-        <v>16.539455100000001</v>
+        <v>16.453249799999998</v>
       </c>
       <c r="F63" s="2">
-        <v>107.4709349</v>
+        <v>107.56329409999999</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>11</v>
@@ -3096,22 +3079,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E64" s="2">
-        <v>16.453249799999998</v>
+        <v>16.5217578</v>
       </c>
       <c r="F64" s="2">
-        <v>107.56329409999999</v>
+        <v>107.57747569999999</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>11</v>
@@ -3123,22 +3106,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E65" s="2">
-        <v>16.5217578</v>
+        <v>16.5582703</v>
       </c>
       <c r="F65" s="2">
-        <v>107.57747569999999</v>
+        <v>107.46912589999999</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>11</v>
@@ -3150,22 +3133,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E66" s="2">
-        <v>16.5582703</v>
+        <v>16.498332099999999</v>
       </c>
       <c r="F66" s="2">
-        <v>107.46912589999999</v>
+        <v>107.5798678</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>11</v>
@@ -3177,22 +3160,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E67" s="2">
-        <v>16.498332099999999</v>
+        <v>16.5053321</v>
       </c>
       <c r="F67" s="2">
-        <v>107.5798678</v>
+        <v>107.5785503</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>11</v>
@@ -3204,22 +3187,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E68" s="2">
-        <v>16.5053321</v>
+        <v>16.507373300000001</v>
       </c>
       <c r="F68" s="2">
-        <v>107.5785503</v>
+        <v>107.63578459999999</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>11</v>
@@ -3231,22 +3214,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2">
-        <v>16.507373300000001</v>
+        <v>16.411297399999999</v>
       </c>
       <c r="F69" s="2">
-        <v>107.63578459999999</v>
+        <v>107.5738937</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>11</v>
@@ -3258,22 +3241,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E70" s="2">
-        <v>16.411297399999999</v>
+        <v>16.462172800000001</v>
       </c>
       <c r="F70" s="2">
-        <v>107.5738937</v>
+        <v>107.57073629999999</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>11</v>
@@ -3285,22 +3268,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E71" s="2">
-        <v>16.453250400000002</v>
+        <v>16.433186800000001</v>
       </c>
       <c r="F71" s="2">
-        <v>107.544583</v>
+        <v>107.56539979999999</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>11</v>
@@ -3312,22 +3295,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="E72" s="2">
-        <v>16.462172800000001</v>
+        <v>16.451093700000001</v>
       </c>
       <c r="F72" s="2">
-        <v>107.57073629999999</v>
+        <v>107.5931525</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>11</v>
@@ -3339,22 +3322,22 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E73" s="2">
-        <v>16.433186800000001</v>
+        <v>16.4566552</v>
       </c>
       <c r="F73" s="2">
-        <v>107.56539979999999</v>
+        <v>107.58094629999999</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>11</v>
@@ -3366,22 +3349,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="E74" s="2">
-        <v>16.451093700000001</v>
+        <v>16.457212599999998</v>
       </c>
       <c r="F74" s="2">
-        <v>107.5931525</v>
+        <v>107.5788716</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>11</v>
@@ -3393,22 +3376,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E75" s="2">
-        <v>16.4566552</v>
+        <v>16.4669715</v>
       </c>
       <c r="F75" s="2">
-        <v>107.58094629999999</v>
+        <v>107.5895601</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>11</v>
@@ -3420,22 +3403,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E76" s="2">
-        <v>16.457212599999998</v>
+        <v>16.459246700000001</v>
       </c>
       <c r="F76" s="2">
-        <v>107.5788716</v>
+        <v>107.5822457</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>11</v>
@@ -3447,22 +3430,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E77" s="2">
-        <v>16.4669715</v>
+        <v>16.467682400000001</v>
       </c>
       <c r="F77" s="2">
-        <v>107.5895601</v>
+        <v>107.57918340000001</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>11</v>
@@ -3474,22 +3457,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E78" s="2">
-        <v>16.459246700000001</v>
+        <v>16.470303600000001</v>
       </c>
       <c r="F78" s="2">
-        <v>107.5822457</v>
+        <v>107.57848389999999</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>11</v>
@@ -3501,22 +3484,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="2">
-        <v>16.467682400000001</v>
+        <v>16.467545900000001</v>
       </c>
       <c r="F79" s="2">
-        <v>107.57918340000001</v>
+        <v>107.57642869999999</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>11</v>
@@ -3528,22 +3511,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E80" s="2">
-        <v>16.470303600000001</v>
+        <v>16.4699025</v>
       </c>
       <c r="F80" s="2">
-        <v>107.57848389999999</v>
+        <v>107.5803251</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>11</v>
@@ -3555,22 +3538,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E81" s="2">
-        <v>16.467545900000001</v>
+        <v>16.470199099999999</v>
       </c>
       <c r="F81" s="2">
-        <v>107.57642869999999</v>
+        <v>107.5800933</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>11</v>
@@ -3582,22 +3565,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E82" s="2">
-        <v>16.4699025</v>
+        <v>16.470616199999998</v>
       </c>
       <c r="F82" s="2">
-        <v>107.5803251</v>
+        <v>107.5797647</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>11</v>
@@ -3609,22 +3592,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="2">
-        <v>16.470199099999999</v>
+        <v>16.468891599999999</v>
       </c>
       <c r="F83" s="2">
-        <v>107.5800933</v>
+        <v>107.5754008</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>11</v>
@@ -3636,22 +3619,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E84" s="2">
-        <v>16.470616199999998</v>
+        <v>16.469718199999999</v>
       </c>
       <c r="F84" s="2">
-        <v>107.5797647</v>
+        <v>107.5746783</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>11</v>
@@ -3663,22 +3646,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E85" s="2">
-        <v>16.468891599999999</v>
+        <v>16.4663574</v>
       </c>
       <c r="F85" s="2">
-        <v>107.5754008</v>
+        <v>107.5802462</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>11</v>
@@ -3690,22 +3673,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E86" s="2">
-        <v>16.469718199999999</v>
+        <v>16.468033299999998</v>
       </c>
       <c r="F86" s="2">
-        <v>107.5746783</v>
+        <v>107.58556849999999</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>11</v>
@@ -3717,22 +3700,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E87" s="2">
-        <v>16.4663574</v>
+        <v>16.459624900000001</v>
       </c>
       <c r="F87" s="2">
-        <v>107.5802462</v>
+        <v>107.5811082</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>11</v>
@@ -3744,22 +3727,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E88" s="2">
-        <v>16.468033299999998</v>
+        <v>16.466781699999999</v>
       </c>
       <c r="F88" s="2">
-        <v>107.58556849999999</v>
+        <v>107.6421227</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>11</v>
@@ -3771,22 +3754,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E89" s="2">
-        <v>16.459624900000001</v>
+        <v>16.471596000000002</v>
       </c>
       <c r="F89" s="2">
-        <v>107.5811082</v>
+        <v>107.5800406</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>11</v>
@@ -3798,22 +3781,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E90" s="2">
-        <v>16.466781699999999</v>
+        <v>16.470597699999999</v>
       </c>
       <c r="F90" s="2">
-        <v>107.6421227</v>
+        <v>107.5824866</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>11</v>
@@ -3825,22 +3808,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E91" s="2">
-        <v>16.471596000000002</v>
+        <v>16.468743400000001</v>
       </c>
       <c r="F91" s="2">
-        <v>107.5800406</v>
+        <v>107.5783867</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>197</v>
+        <v>329</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>11</v>
@@ -3852,22 +3835,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E92" s="2">
-        <v>16.470597699999999</v>
+        <v>16.468038</v>
       </c>
       <c r="F92" s="2">
-        <v>107.5824866</v>
+        <v>107.5750678</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>11</v>
@@ -3879,22 +3862,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E93" s="2">
-        <v>16.468743400000001</v>
+        <v>16.470085000000001</v>
       </c>
       <c r="F93" s="2">
-        <v>107.5783867</v>
+        <v>107.57521970000001</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>11</v>
@@ -3906,22 +3889,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E94" s="2">
-        <v>16.468038</v>
+        <v>16.475617100000001</v>
       </c>
       <c r="F94" s="2">
-        <v>107.5750678</v>
+        <v>107.5806219</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>11</v>
@@ -3933,22 +3916,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E95" s="2">
-        <v>16.470085000000001</v>
+        <v>16.471959300000002</v>
       </c>
       <c r="F95" s="2">
-        <v>107.57521970000001</v>
+        <v>107.583647</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>11</v>
@@ -3960,22 +3943,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E96" s="2">
-        <v>16.475617100000001</v>
+        <v>16.469853499999999</v>
       </c>
       <c r="F96" s="2">
-        <v>107.5806219</v>
+        <v>107.5825025</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>11</v>
@@ -3987,22 +3970,22 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E97" s="2">
-        <v>16.471959300000002</v>
+        <v>16.471307299999999</v>
       </c>
       <c r="F97" s="2">
-        <v>107.583647</v>
+        <v>107.5819424</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>11</v>
@@ -4014,22 +3997,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E98" s="2">
-        <v>16.469853499999999</v>
+        <v>16.472959299999999</v>
       </c>
       <c r="F98" s="2">
-        <v>107.5825025</v>
+        <v>107.58079309999999</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>11</v>
@@ -4041,22 +4024,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E99" s="2">
-        <v>16.471307299999999</v>
+        <v>16.4779515</v>
       </c>
       <c r="F99" s="2">
-        <v>107.5819424</v>
+        <v>107.5875648</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>11</v>
@@ -4068,22 +4051,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E100" s="2">
-        <v>16.472959299999999</v>
+        <v>16.452861200000001</v>
       </c>
       <c r="F100" s="2">
-        <v>107.58079309999999</v>
+        <v>107.58766319999999</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>11</v>
@@ -4095,81 +4078,29 @@
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E101" s="2">
-        <v>16.4779515</v>
+        <v>16.4715813</v>
       </c>
       <c r="F101" s="2">
-        <v>107.5875648</v>
+        <v>107.5763379</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <f t="shared" si="0"/>
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E102" s="2">
-        <v>16.452861200000001</v>
-      </c>
-      <c r="F102" s="2">
-        <v>107.58766319999999</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E103" s="2">
-        <v>16.4715813</v>
-      </c>
-      <c r="F103" s="2">
-        <v>107.5763379</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="102" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="104" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="105" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="106" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5065,11 +4996,9 @@
     <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5083,21 +5012,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C2" s="2">
         <v>5</v>
@@ -5105,10 +5034,10 @@
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C3" s="2">
         <v>92</v>
@@ -5116,10 +5045,10 @@
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C4" s="2">
         <v>52</v>
@@ -5127,10 +5056,10 @@
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C5" s="2">
         <v>63</v>
@@ -5138,10 +5067,10 @@
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2">
         <v>90</v>
@@ -5149,10 +5078,10 @@
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2">
         <v>70</v>
@@ -5160,10 +5089,10 @@
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C8" s="2">
         <v>80</v>
@@ -5171,10 +5100,10 @@
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C9" s="2">
         <v>10</v>
@@ -5182,10 +5111,10 @@
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C10" s="2">
         <v>50</v>
@@ -5193,10 +5122,10 @@
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C11" s="2">
         <v>56</v>
@@ -5204,10 +5133,10 @@
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C12" s="2">
         <v>17</v>
@@ -5215,10 +5144,10 @@
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C13" s="2">
         <v>30</v>
@@ -5226,10 +5155,10 @@
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C14" s="2">
         <v>19</v>
@@ -5237,10 +5166,10 @@
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C15" s="2">
         <v>87</v>
@@ -5248,10 +5177,10 @@
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C16" s="2">
         <v>7</v>
@@ -5259,10 +5188,10 @@
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C17" s="2">
         <v>78</v>
@@ -5270,10 +5199,10 @@
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C18" s="2">
         <v>16</v>
@@ -5281,10 +5210,10 @@
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2">
         <v>72</v>
@@ -5292,10 +5221,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2">
         <v>92</v>
@@ -5303,10 +5232,10 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2">
         <v>54</v>
@@ -5314,10 +5243,10 @@
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2">
         <v>14</v>
@@ -5325,10 +5254,10 @@
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2">
         <v>12</v>
@@ -5336,10 +5265,10 @@
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2">
         <v>50</v>
@@ -5347,10 +5276,10 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C25" s="2">
         <v>49</v>
@@ -5358,10 +5287,10 @@
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C26" s="2">
         <v>95</v>
@@ -5369,10 +5298,10 @@
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2">
         <v>79</v>
@@ -5380,10 +5309,10 @@
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2">
         <v>75</v>
@@ -5391,10 +5320,10 @@
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2">
         <v>13</v>
@@ -5402,10 +5331,10 @@
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C30" s="2">
         <v>16</v>
@@ -5413,10 +5342,10 @@
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2">
         <v>22</v>
@@ -5424,10 +5353,10 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2">
         <v>29</v>
@@ -5435,10 +5364,10 @@
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2">
         <v>83</v>
@@ -5446,10 +5375,10 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C34" s="2">
         <v>54</v>
@@ -5457,10 +5386,10 @@
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C35" s="2">
         <v>60</v>
@@ -5468,10 +5397,10 @@
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C36" s="2">
         <v>26</v>
@@ -5479,10 +5408,10 @@
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C37" s="2">
         <v>17</v>
@@ -5490,10 +5419,10 @@
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C38" s="2">
         <v>53</v>
@@ -5501,10 +5430,10 @@
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C39" s="2">
         <v>20</v>
@@ -5512,10 +5441,10 @@
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C40" s="2">
         <v>12</v>
@@ -5523,10 +5452,10 @@
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C41" s="2">
         <v>84</v>
@@ -5534,10 +5463,10 @@
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2">
         <v>95</v>
@@ -5545,10 +5474,10 @@
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C43" s="2">
         <v>35</v>
@@ -5556,10 +5485,10 @@
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2">
         <v>32</v>
@@ -5567,10 +5496,10 @@
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C45" s="2">
         <v>99</v>
@@ -5578,10 +5507,10 @@
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2">
         <v>32</v>
@@ -5589,10 +5518,10 @@
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C47" s="2">
         <v>17</v>
@@ -5600,10 +5529,10 @@
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2">
         <v>39</v>
@@ -5611,10 +5540,10 @@
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2">
         <v>70</v>
@@ -5622,10 +5551,10 @@
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2">
         <v>54</v>
@@ -5633,10 +5562,10 @@
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2">
         <v>47</v>
@@ -5644,10 +5573,10 @@
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C52" s="2">
         <v>38</v>
@@ -5655,10 +5584,10 @@
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C53" s="2">
         <v>92</v>
@@ -5666,10 +5595,10 @@
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2">
         <v>31</v>
@@ -5677,10 +5606,10 @@
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C55" s="2">
         <v>86</v>
@@ -5688,10 +5617,10 @@
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C56" s="2">
         <v>42</v>
@@ -5699,10 +5628,10 @@
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C57" s="2">
         <v>16</v>
@@ -5710,10 +5639,10 @@
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C58" s="2">
         <v>73</v>
@@ -5721,10 +5650,10 @@
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C59" s="2">
         <v>36</v>
@@ -5732,10 +5661,10 @@
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C60" s="2">
         <v>7</v>
@@ -5743,10 +5672,10 @@
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C61" s="2">
         <v>11</v>
@@ -5754,10 +5683,10 @@
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C62" s="2">
         <v>89</v>
@@ -5765,10 +5694,10 @@
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C63" s="2">
         <v>98</v>
@@ -5776,10 +5705,10 @@
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2">
         <v>71</v>
@@ -5787,10 +5716,10 @@
     </row>
     <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2">
         <v>75</v>
@@ -5798,10 +5727,10 @@
     </row>
     <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C66" s="2">
         <v>93</v>
@@ -5809,10 +5738,10 @@
     </row>
     <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C67" s="2">
         <v>25</v>
@@ -5820,10 +5749,10 @@
     </row>
     <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C68" s="2">
         <v>39</v>
@@ -5831,10 +5760,10 @@
     </row>
     <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C69" s="2">
         <v>76</v>
@@ -5842,10 +5771,10 @@
     </row>
     <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C70" s="2">
         <v>23</v>
@@ -5853,10 +5782,10 @@
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C71" s="2">
         <v>77</v>
@@ -5864,10 +5793,10 @@
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C72" s="2">
         <v>29</v>
@@ -5875,10 +5804,10 @@
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C73" s="2">
         <v>40</v>
@@ -5886,10 +5815,10 @@
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C74" s="2">
         <v>101</v>
@@ -5897,10 +5826,10 @@
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C75" s="2">
         <v>41</v>
@@ -5908,10 +5837,10 @@
     </row>
     <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C76" s="2">
         <v>5</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Locations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Likes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,696 +415,696 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>image</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>city</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hoàng Thành Huế</t>
+          <t>Bi Đình</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hoàng Thành Huế là di sản UNESCO, nổi bật với kiến trúc cổ kính và lịch sử triều Nguyễn đặc sắc giữa lòng cố đô.</t>
+          <t>Bi Đình là điểm dừng chân yên bình giữa thiên nhiên, nổi bật với kiến trúc cổ kính và không gian thanh tịnh.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>16.46883</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>107.57815</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>/static/images/hoang-thanh-hue.png</t>
-        </is>
+        <v>16.4331868</v>
+      </c>
+      <c r="G2" t="n">
+        <v>107.5653998</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bi-dinh.png</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cung An Định</t>
+          <t>Bãi biển Lăng Cô</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cung An Định là công trình kiến trúc độc đáo, hòa quyện giữa phong cách Á - Âu, nằm bên dòng sông An Cựu thơ mộng ở Huế.</t>
+          <t>Bãi biển Lăng Cô sở hữu cát trắng mịn, nước biển trong xanh, là điểm đến lý tưởng cho du khách yêu thiên nhiên và nghỉ dưỡng.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>16.45722</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bãi biển</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>107.59802</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>/static/images/cung-an-dinh.png</t>
-        </is>
+        <v>16.26424</v>
+      </c>
+      <c r="G3" t="n">
+        <v>108.06582</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bai-bien-lang-co.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Đàn Nam Giao</t>
+          <t>Bãi biển Thuận An</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Đàn Nam Giao là nơi triều Nguyễn tổ chức lễ tế trời linh thiêng, mang đậm dấu ấn văn hóa tâm linh cố đô Huế.</t>
+          <t>Bãi biển Thuận An nổi bật với cát trắng mịn, nước biển trong xanh và không khí yên bình, lý tưởng cho kỳ nghỉ thư giãn.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>16.4378</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bãi biển</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>107.5827</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>/static/images/dan-nam-giao.png</t>
-        </is>
+        <v>16.55966</v>
+      </c>
+      <c r="G4" t="n">
+        <v>107.65428</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bai-bien-thuan-an.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chùa Thiên Mụ</t>
+          <t>Bún Bò Mệ Kéo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chùa Thiên Mụ cổ kính bên sông Hương, nổi bật với tháp Phước Duyên, là biểu tượng tâm linh và điểm đến hấp dẫn của Huế.</t>
+          <t>Bún Bò Mệ Kéo nổi tiếng với nước dùng đậm đà, thịt bò mềm thơm, là điểm dừng chân không thể bỏ lỡ khi đến Huế.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>16.4537</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>107.54458</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>/static/images/chua-thien-mu.png</t>
-        </is>
+        <v>16.47505</v>
+      </c>
+      <c r="G5" t="n">
+        <v>107.5887</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bun-bo-me-keo.png</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chùa Từ Đàm</t>
+          <t>Bảo tàng Cổ vật Cung đình Huế</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chùa Từ Đàm là ngôi chùa cổ kính, thanh tịnh, nổi bật với kiến trúc độc đáo và không gian yên bình giữa lòng thành phố Huế.</t>
+          <t>Bảo tàng Cổ vật Cung đình Huế lưu giữ nhiều báu vật triều Nguyễn, phản ánh nét đẹp văn hóa cung đình xưa giữa không gian cổ kính.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>16.45153</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>107.58178</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>/static/images/chua-tu-dam.png</t>
-        </is>
+        <v>16.4713073</v>
+      </c>
+      <c r="G6" t="n">
+        <v>107.5819424</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bao-tang-co-vat-cung-dinh-hue.png</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chùa Báo Quốc</t>
+          <t>Bảo tàng Hồ Chí Minh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chùa Báo Quốc là ngôi chùa cổ kính, yên bình giữa lòng Huế, nổi bật với kiến trúc truyền thống và không gian thanh tịnh.</t>
+          <t>Bảo tàng Hồ Chí Minh lưu giữ nhiều hiện vật, tư liệu quý về cuộc đời và sự nghiệp của Chủ tịch Hồ Chí Minh, thu hút đông đảo du khách tham quan.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>16.45421</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>107.57962</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>/static/images/chua-bao-quoc.png</t>
-        </is>
+        <v>16.4596249</v>
+      </c>
+      <c r="G7" t="n">
+        <v>107.5811082</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bao-tang-ho-chi-minh.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chùa Từ Hiếu</t>
+          <t>Bảo tàng Lịch sử Thừa Thiên Huế</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chùa Từ Hiếu là ngôi chùa cổ kính, yên bình giữa rừng thông, nổi tiếng với kiến trúc độc đáo và không gian thanh tịnh ở Huế.</t>
+          <t>Bảo tàng Lịch sử Thừa Thiên Huế lưu giữ nhiều hiện vật quý, tái hiện lịch sử và văn hóa đặc sắc của vùng đất cố đô.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>16.43889</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>107.57199</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>/static/images/chua-tu-hieu.png</t>
-        </is>
+        <v>16.4698535</v>
+      </c>
+      <c r="G8" t="n">
+        <v>107.5825025</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bao-tang-lich-su-thua-thien-hue.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chùa Huyền Không Sơn Thượng</t>
+          <t>Bắc Khuyết Đài</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chùa Huyền Không Sơn Thượng ẩn mình giữa núi rừng Huế, mang vẻ đẹp thanh tịnh, yên bình, lý tưởng cho những ai tìm kiếm sự an lạc.</t>
+          <t>Bắc Khuyết Đài: điểm check-in nổi tiếng với kiến trúc độc đáo, view biển tuyệt đẹp và không gian yên bình giữa lòng Đà Nẵng.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>16.45078</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>107.49381</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>/static/images/chua-huyen-khong-son-thuong.png</t>
-        </is>
+        <v>16.4719956</v>
+      </c>
+      <c r="G9" t="n">
+        <v>107.5758125</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/bac-khuyet-dai.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chùa Thiền Lâm</t>
+          <t>Bối Lăng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chùa Thiền Lâm nổi bật với kiến trúc độc đáo, không gian yên bình, là điểm đến tâm linh hấp dẫn giữa lòng cố đô Huế.</t>
+          <t>Bối Lăng là quần thể lăng mộ cổ kính, yên bình giữa rừng thông, lưu giữ dấu ấn triều đại nhà Lý tại Bắc Ninh.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>16.43817</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>107.57528</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>/static/images/chua-thien-lam.png</t>
-        </is>
+        <v>16.4342482</v>
+      </c>
+      <c r="G10" t="n">
+        <v>107.5666428</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/boi-lang.png</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Điện Hòn Chén</t>
+          <t>Chè Hẻm Huế</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Điện Hòn Chén là điểm du lịch tâm linh nổi tiếng bên sông Hương, thu hút du khách bởi kiến trúc độc đáo và không gian linh thiêng.</t>
+          <t>Chè Hẻm Huế – hương vị ngọt thanh, đa dạng topping, thưởng thức trong không gian bình dị giữa lòng phố cổ.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>16.42195</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>107.56296</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>/static/images/dien-hon-chen.png</t>
-        </is>
+        <v>16.4651</v>
+      </c>
+      <c r="G11" t="n">
+        <v>107.59358</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/che-hem-hue.png</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lăng Khải Định</t>
+          <t>Chùa Báo Quốc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lăng Khải Định là công trình lăng tẩm độc đáo, kết hợp kiến trúc Đông Tây tinh xảo giữa núi non thơ mộng xứ Huế.</t>
+          <t>Chùa Báo Quốc là ngôi chùa cổ kính, yên bình giữa lòng Huế, nổi bật với kiến trúc truyền thống và không gian thanh tịnh.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>16.3989</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>107.59029</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>/static/images/lang-khai-dinh.png</t>
-        </is>
+        <v>16.45421</v>
+      </c>
+      <c r="G12" t="n">
+        <v>107.57962</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-bao-quoc.png</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lăng Tự Đức</t>
+          <t>Chùa Diệu Đế</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lăng Tự Đức là quần thể lăng tẩm thơ mộng, hòa quyện giữa kiến trúc tinh tế và thiên nhiên hữu tình tại cố đô Huế.</t>
+          <t>Chùa Diệu Đế là ngôi chùa cổ kính bên sông Hương, nổi bật với kiến trúc độc đáo và không gian thanh tịnh giữa lòng Huế.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>16.43299</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>107.56644</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>/static/images/lang-tu-duc.png</t>
-        </is>
+        <v>16.4779515</v>
+      </c>
+      <c r="G13" t="n">
+        <v>107.5875648</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-dieu-de.png</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lăng Minh Mạng</t>
+          <t>Chùa Huyền Không Sơn Thượng</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lăng Minh Mạng là công trình kiến trúc uy nghi, hòa quyện thiên nhiên và nghệ thuật, nằm giữa không gian xanh mát của cố đô Huế.</t>
+          <t>Chùa Huyền Không Sơn Thượng ẩn mình giữa núi rừng Huế, mang vẻ đẹp thanh tịnh, yên bình, lý tưởng cho những ai tìm kiếm sự an lạc.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>16.38748</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>107.57025</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>/static/images/lang-minh-mang.png</t>
-        </is>
+        <v>16.45078</v>
+      </c>
+      <c r="G14" t="n">
+        <v>107.49381</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-huyen-khong-son-thuong.png</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lăng Gia Long</t>
+          <t>Chùa Thiên Mụ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lăng Gia Long là quần thể lăng tẩm uy nghi giữa núi rừng, hòa quyện thiên nhiên và kiến trúc độc đáo của triều Nguyễn.</t>
+          <t>Chùa Thiên Mụ cổ kính bên sông Hương, nổi bật với tháp Phước Duyên, là biểu tượng tâm linh và điểm đến hấp dẫn của Huế.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>16.36197</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>107.59694</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>/static/images/lang-gia-long.png</t>
-        </is>
+        <v>16.4537</v>
+      </c>
+      <c r="G15" t="n">
+        <v>107.54458</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-thien-mu.png</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bún Bò Mệ Kéo</t>
+          <t>Chùa Thiền Lâm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bún Bò Mệ Kéo nổi tiếng với nước dùng đậm đà, thịt bò mềm thơm, là điểm dừng chân không thể bỏ lỡ khi đến Huế.</t>
+          <t>Chùa Thiền Lâm nổi bật với kiến trúc độc đáo, không gian yên bình, là điểm đến tâm linh hấp dẫn giữa lòng cố đô Huế.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ẩm thực</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>16.47505</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>107.5887</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>/static/images/bun-bo-me-keo.png</t>
-        </is>
+        <v>16.43817</v>
+      </c>
+      <c r="G16" t="n">
+        <v>107.57528</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-thien-lam.png</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chè Hẻm Huế</t>
+          <t>Chùa Từ Hiếu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chè Hẻm Huế – hương vị ngọt thanh, đa dạng topping, thưởng thức trong không gian bình dị giữa lòng phố cổ.</t>
+          <t>Chùa Từ Hiếu là ngôi chùa cổ kính, yên bình giữa rừng thông, nổi tiếng với kiến trúc độc đáo và không gian thanh tịnh ở Huế.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ẩm thực</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16.4651</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>107.59358</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>/static/images/che-hem-hue.png</t>
-        </is>
+        <v>16.43889</v>
+      </c>
+      <c r="G17" t="n">
+        <v>107.57199</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-tu-hieu.png</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nem Lụi Bà Tý</t>
+          <t>Chùa Từ Đàm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nem Lụi Bà Tý thơm ngon, đậm vị, nướng than hồng, ăn kèm rau sống và nước chấm đặc biệt, là trải nghiệm ẩm thực Huế khó quên.</t>
+          <t>Chùa Từ Đàm là ngôi chùa cổ kính, thanh tịnh, nổi bật với kiến trúc độc đáo và không gian yên bình giữa lòng thành phố Huế.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ẩm thực</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>16.48003</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>107.58339</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>/static/images/nem-lui-ba-ty.png</t>
-        </is>
+        <v>16.45153</v>
+      </c>
+      <c r="G18" t="n">
+        <v>107.58178</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/chua-tu-dam.png</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chợ Đông Ba</t>
+          <t>Chợ An Cựu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chợ Đông Ba là trung tâm mua sắm sầm uất, nơi du khách khám phá ẩm thực và đặc sản Huế truyền thống.</t>
+          <t>Chợ An Cựu nhộn nhịp, đa dạng ẩm thực và hàng hóa, là điểm đến hấp dẫn để khám phá nét văn hóa đặc trưng của Huế.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Mua sắm</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>16.47243</v>
-      </c>
       <c r="F19" t="n">
-        <v>107.58867</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>/static/images/cho-dong-ba.png</t>
-        </is>
+        <v>16.45745</v>
+      </c>
+      <c r="G19" t="n">
+        <v>107.6007</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cho-an-cuu.png</t>
         </is>
       </c>
     </row>
@@ -1134,383 +1124,383 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Mua sắm</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>16.45518</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>107.58394</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>/static/images/cho-ben-ngu.png</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Huế</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chợ An Cựu</t>
+          <t>Chợ Tây Lộc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chợ An Cựu nhộn nhịp, đa dạng ẩm thực và hàng hóa, là điểm đến hấp dẫn để khám phá nét văn hóa đặc trưng của Huế.</t>
+          <t>Chợ Tây Lộc là điểm đến sôi động, đậm chất Huế với nhiều món ăn ngon và không khí nhộn nhịp, thân thiện.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Mua sắm</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>16.45745</v>
-      </c>
       <c r="F21" t="n">
-        <v>107.6007</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>/static/images/cho-an-cuu.png</t>
-        </is>
+        <v>16.47678</v>
+      </c>
+      <c r="G21" t="n">
+        <v>107.56569</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cho-tay-loc.png</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chợ Tây Lộc</t>
+          <t>Chợ Xép</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chợ Tây Lộc là điểm đến sôi động, đậm chất Huế với nhiều món ăn ngon và không khí nhộn nhịp, thân thiện.</t>
+          <t>Chợ Xép là điểm đến sôi động, đậm chất địa phương với nhiều món ăn ngon và không khí nhộn nhịp mỗi sáng.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Mua sắm</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>16.47678</v>
-      </c>
       <c r="F22" t="n">
-        <v>107.56569</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>/static/images/cho-tay-loc.png</t>
-        </is>
+        <v>16.47888</v>
+      </c>
+      <c r="G22" t="n">
+        <v>107.58242</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cho-xep.png</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chợ Xép</t>
+          <t>Chợ Đông Ba</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chợ Xép là điểm đến sôi động, đậm chất địa phương với nhiều món ăn ngon và không khí nhộn nhịp mỗi sáng.</t>
+          <t>Chợ Đông Ba là trung tâm mua sắm sầm uất, nơi du khách khám phá ẩm thực và đặc sản Huế truyền thống.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Mua sắm</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>16.47888</v>
-      </c>
       <c r="F23" t="n">
-        <v>107.58242</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>/static/images/cho-xep.png</t>
-        </is>
+        <v>16.47243</v>
+      </c>
+      <c r="G23" t="n">
+        <v>107.58867</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cho-dong-ba.png</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nhà vườn An Hiên</t>
+          <t>Cung An Định</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nhà vườn An Hiên là không gian xanh mát, yên bình, mang đậm nét kiến trúc và văn hóa truyền thống xứ Huế.</t>
+          <t>Cung An Định là công trình kiến trúc độc đáo, hòa quyện giữa phong cách Á - Âu, nằm bên dòng sông An Cựu thơ mộng ở Huế.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>16.45532</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>107.55378</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>/static/images/nha-vuon-an-hien.png</t>
-        </is>
+        <v>16.45722</v>
+      </c>
+      <c r="G24" t="n">
+        <v>107.59802</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cung-an-dinh.png</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cầu Trường Tiền</t>
+          <t>Cung Diên Thọ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cầu Trường Tiền bắc qua sông Hương, là biểu tượng thơ mộng và lịch sử nổi bật của thành phố Huế.</t>
+          <t>Cung Diên Thọ là nơi nghỉ ngơi của Hoàng thái hậu, nổi bật với kiến trúc cổ kính và không gian yên bình trong Đại Nội Huế.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>16.46912</v>
-      </c>
       <c r="F25" t="n">
-        <v>107.58859</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>/static/images/cau-truong-tien.png</t>
-        </is>
+        <v>16.4688916</v>
+      </c>
+      <c r="G25" t="n">
+        <v>107.5754008</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cung-dien-tho.png</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sông Hương</t>
+          <t>Cung Trường Sanh</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sông Hương thơ mộng uốn lượn giữa lòng Huế, phản chiếu vẻ đẹp trầm mặc và lãng mạn của cố đô.</t>
+          <t>Cung Trường Sanh là công trình cổ kính, yên bình giữa Đại Nội Huế, nổi bật với kiến trúc độc đáo và không gian xanh mát.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>16.47021</v>
-      </c>
       <c r="F26" t="n">
-        <v>107.59024</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>/static/images/song-huong.png</t>
-        </is>
+        <v>16.4697182</v>
+      </c>
+      <c r="G26" t="n">
+        <v>107.5746783</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cung-truong-sanh.png</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cầu ngói Thanh Toàn</t>
+          <t>Công viên Hồ Thủy Tiên</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cầu ngói Thanh Toàn là cây cầu cổ kính, độc đáo, nằm giữa làng quê yên bình, thu hút du khách bởi vẻ đẹp truyền thống và kiến trúc tinh xảo.</t>
+          <t>Công viên Hồ Thủy Tiên là điểm check-in huyền bí với hồ nước, rừng cây và rồng khổng lồ bỏ hoang giữa lòng Huế.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>16.46674</v>
-      </c>
       <c r="F27" t="n">
-        <v>107.6421</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>/static/images/cau-ngoi-thanh-toan.png</t>
-        </is>
+        <v>16.4112974</v>
+      </c>
+      <c r="G27" t="n">
+        <v>107.5738937</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cong-vien-ho-thuy-tien.png</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Làng Hương Thủy Xuân</t>
+          <t>Cầu Châu Sơn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Làng Hương Thủy Xuân nổi tiếng với nghề làm hương truyền thống, sắc màu rực rỡ, thu hút du khách khám phá văn hóa Huế.</t>
+          <t>Cầu Châu Sơn nổi bật với kiến trúc độc đáo, bắc qua sông Đáy, là điểm check-in hấp dẫn tại thành phố Phủ Lý, Hà Nam.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>16.43554</v>
-      </c>
       <c r="F28" t="n">
-        <v>107.56227</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>/static/images/lang-huong-thuy-xuan.png</t>
-        </is>
+        <v>16.4183309</v>
+      </c>
+      <c r="G28" t="n">
+        <v>107.6536678</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-chau-son.png</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Trường THPT chuyên Quốc Học Huế</t>
+          <t>Cầu Chợ Dinh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trường THPT chuyên Quốc Học Huế nổi bật với kiến trúc cổ kính, không gian xanh mát và bề dày lịch sử hơn 125 năm.</t>
+          <t>Cầu Chợ Dinh bắc qua sông Nhật Lệ, là điểm check-in nổi bật với kiến trúc độc đáo và khung cảnh thơ mộng giữa lòng thành phố Đồng Hới.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>16.46008</v>
-      </c>
       <c r="F29" t="n">
-        <v>107.58335</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>/static/images/truong-thpt-chuyen-quoc-hoc-hue.png</t>
-        </is>
+        <v>16.4929675</v>
+      </c>
+      <c r="G29" t="n">
+        <v>107.5924182</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-cho-dinh.png</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ga Huế</t>
+          <t>Cầu Ga</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ga Huế là điểm dừng chân cổ kính, lưu giữ dấu ấn lịch sử giữa lòng thành phố mộng mơ.</t>
+          <t>Cầu Ga nổi bật với kiến trúc độc đáo, là điểm check-in lý tưởng giữa thiên nhiên thơ mộng của Đà Lạt.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>16.45648</v>
-      </c>
       <c r="F30" t="n">
-        <v>107.57805</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>/static/images/ga-hue.png</t>
-        </is>
+        <v>16.4572126</v>
+      </c>
+      <c r="G30" t="n">
+        <v>107.5788716</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-ga.png</t>
         </is>
       </c>
     </row>
@@ -1530,2543 +1520,4725 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>16.46561</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>107.58744</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>/static/images/cau-go-lim.png</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Huế</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Đồi Vọng Cảnh</t>
+          <t>Cầu Tam Giang</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Đồi Vọng Cảnh là điểm ngắm cảnh tuyệt đẹp, nơi du khách chiêm ngưỡng sông Hương và thành phố Huế từ trên cao.</t>
+          <t>Cầu Tam Giang nổi bật giữa thiên nhiên thơ mộng, là điểm check-in lý tưởng ngắm bình minh và hoàng hôn trên phá Tam Giang.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>16.42723</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>107.56493</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>/static/images/doi-vong-canh.png</t>
-        </is>
+        <v>16.5821907</v>
+      </c>
+      <c r="G32" t="n">
+        <v>107.5885002</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-tam-giang.png</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Núi Ngự Bình</t>
+          <t>Cầu Thủy Vân</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Núi Ngự Bình là biểu tượng thiên nhiên thơ mộng của Huế, nổi bật với dáng núi uy nghi và khung cảnh yên bình bên dòng sông Hương.</t>
+          <t>Cầu Thủy Vân nổi bật với kiến trúc hiện đại, là điểm check-in lý tưởng giữa thiên nhiên thơ mộng và dòng sông êm đềm.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>16.44168</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>107.5961</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>/static/images/nui-ngu-binh.png</t>
-        </is>
+        <v>16.4824922</v>
+      </c>
+      <c r="G33" t="n">
+        <v>107.6040878</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-thuy-van.png</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Đầm Lập An</t>
+          <t>Cầu Trường Tiền</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Đầm Lập An là viên ngọc xanh giữa lòng núi, nổi bật với mặt nước phẳng lặng và cảnh sắc thơ mộng, lý tưởng để thư giãn và chụp ảnh.</t>
+          <t>Cầu Trường Tiền bắc qua sông Hương, là biểu tượng thơ mộng và lịch sử nổi bật của thành phố Huế.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>16.22142</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>108.06157</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>/static/images/dam-lap-an.png</t>
-        </is>
+        <v>16.46912</v>
+      </c>
+      <c r="G34" t="n">
+        <v>107.58859</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-truong-tien.png</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vườn Quốc gia Bạch Mã</t>
+          <t>Cầu Vân Dương</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vườn Quốc gia Bạch Mã nổi bật với rừng nguyên sinh, thác nước hùng vĩ và hệ động thực vật đa dạng, lý tưởng cho du lịch sinh thái.</t>
+          <t>Cầu Vân Dương nổi bật với kiến trúc hiện đại, nối liền hai bờ sông, là điểm check-in lý tưởng khi đến Quảng Trị.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>16.2165</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>107.89365</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>/static/images/vuon-quoc-gia-bach-ma.png</t>
-        </is>
+        <v>16.4741464</v>
+      </c>
+      <c r="G35" t="n">
+        <v>107.6078971</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-van-duong.png</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rừng ngập mặn Rú Chá</t>
+          <t>Cầu Vĩ Dạ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Khám phá Rú Chá - rừng ngập mặn nguyên sinh độc đáo, hòa mình vào thiên nhiên hoang sơ và tận hưởng không khí trong lành ven phá Tam Giang.</t>
+          <t>Cầu Vĩ Dạ bắc qua sông An Cựu, nổi bật với vẻ đẹp thơ mộng, gắn liền thi ca và ký ức xứ Huế.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>16.55748</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>107.61144</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>/static/images/rung-ngap-man-ru-cha.png</t>
-        </is>
+        <v>16.4714657</v>
+      </c>
+      <c r="G36" t="n">
+        <v>107.5997497</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-vi-da.png</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Phá Tam Giang</t>
+          <t>Cầu ngói Thanh Toàn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phá Tam Giang là đầm nước lợ lớn nhất Đông Nam Á, nổi bật với cảnh hoàng hôn tuyệt đẹp và trải nghiệm chèo thuyền độc đáo.</t>
+          <t>Cầu ngói Thanh Toàn là cây cầu cổ kính, độc đáo, nằm giữa làng quê yên bình, thu hút du khách bởi vẻ đẹp truyền thống và kiến trúc tinh xảo.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>16.59788</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>107.54309</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>/static/images/pha-tam-giang.png</t>
-        </is>
+        <v>16.46674</v>
+      </c>
+      <c r="G37" t="n">
+        <v>107.6421</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cau-ngoi-thanh-toan.png</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suối Voi</t>
+          <t>Cửu Vị Thần Công</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Suối Voi là điểm đến hoang sơ, nước trong xanh, cảnh sắc thiên nhiên tuyệt đẹp, lý tưởng để thư giãn và khám phá giữa núi rừng Huế.</t>
+          <t>Cửu Vị Thần Công là bộ súng thần công nổi tiếng, biểu tượng lịch sử oai hùng tại Đại Nội Huế, thu hút du khách tham quan và tìm hiểu.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Thiên nhiên</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>16.24387</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>107.98943</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>/static/images/suoi-voi.png</t>
-        </is>
+        <v>16.4679198</v>
+      </c>
+      <c r="G38" t="n">
+        <v>107.5812344</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/cuu-vi-than-cong.png</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bãi biển Lăng Cô</t>
+          <t>Di tích Nhà Lưu niệm Chủ tịch Hồ Chí Minh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bãi biển Lăng Cô sở hữu cát trắng mịn, nước biển trong xanh, là điểm đến lý tưởng cho du khách yêu thiên nhiên và nghỉ dưỡng.</t>
+          <t>Di tích Nhà Lưu niệm Chủ tịch Hồ Chí Minh là nơi lưu giữ kỷ vật, tái hiện cuộc sống giản dị của Bác tại quê hương.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bãi biển</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>16.26424</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>108.06582</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>/static/images/bai-bien-lang-co.png</t>
-        </is>
+        <v>16.4756171</v>
+      </c>
+      <c r="G39" t="n">
+        <v>107.5806219</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/di-tich-nha-luu-niem-chu-tich-ho-chi-minh.png</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bãi biển Thuận An</t>
+          <t>Duyệt Thị Đường</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bãi biển Thuận An nổi bật với cát trắng mịn, nước biển trong xanh và không khí yên bình, lý tưởng cho kỳ nghỉ thư giãn.</t>
+          <t>Duyệt Thị Đường là nhà hát cổ kính trong Hoàng thành Thăng Long, nơi lưu giữ nghệ thuật múa rối nước truyền thống Việt Nam.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bãi biển</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>16.55966</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>107.65428</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>/static/images/bai-bien-thuan-an.png</t>
-        </is>
+        <v>16.4703036</v>
+      </c>
+      <c r="G40" t="n">
+        <v>107.5784839</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/duyet-thi-duong.png</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tử Cấm Thành</t>
+          <t>Ga Huế</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tử Cấm Thành là cung điện cổ kính, biểu tượng quyền lực triều đại Minh - Thanh, nổi bật với kiến trúc nguy nga giữa lòng Bắc Kinh.</t>
+          <t>Ga Huế là điểm dừng chân cổ kính, lưu giữ dấu ấn lịch sử giữa lòng thành phố mộng mơ.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>16.4694914</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F41" t="n">
-        <v>107.577755</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>/static/images/tu-cam-thanh.png</t>
-        </is>
+        <v>16.45648</v>
+      </c>
+      <c r="G41" t="n">
+        <v>107.57805</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/ga-hue.png</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Văn Thánh Huế</t>
+          <t>Hoàng Thành Huế</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Văn Thánh Huế là di tích lịch sử nổi bật, lưu giữ giá trị văn hóa và truyền thống hiếu học của vùng đất cố đô.</t>
+          <t>Hoàng Thành Huế là di sản UNESCO, nổi bật với kiến trúc cổ kính và lịch sử triều Nguyễn đặc sắc giữa lòng cố đô.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>Di tích</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>16.452965</v>
-      </c>
       <c r="F42" t="n">
-        <v>107.538902</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>/static/images/van-thanh-hue.png</t>
-        </is>
+        <v>16.46883</v>
+      </c>
+      <c r="G42" t="n">
+        <v>107.57815</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/hoang-thanh-hue.png</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tượng đài Quan Thế Âm Bồ Tát</t>
+          <t>Hưng Tổ Miếu</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tượng đài Quan Thế Âm Bồ Tát uy nghi giữa thiên nhiên, là điểm đến tâm linh nổi bật thu hút du khách thập phương.</t>
+          <t>Hưng Tổ Miếu là di tích lịch sử linh thiêng, nơi thờ các vị tổ nhà Nguyễn, thu hút du khách bởi kiến trúc cổ kính và không gian yên bình.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>16.3920792</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>107.5841879</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>/static/images/tuong-dai-quan-the-am-bo-tat.png</t>
-        </is>
+        <v>16.4675459</v>
+      </c>
+      <c r="G43" t="n">
+        <v>107.5764287</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/hung-to-mieu.png</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Điềm Phùng Thị</t>
+          <t>Hồ Nội Kim Thủy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Khám phá không gian nghệ thuật độc đáo tại Bảo tàng Điềm Phùng Thị, nơi lưu giữ tinh hoa điêu khắc Việt Nam hiện đại.</t>
+          <t>Hồ Nội Kim Thủy xanh biếc, yên bình giữa núi non, là điểm đến lý tưởng để thư giãn và tận hưởng không khí trong lành.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>16.4578346</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>107.5842155</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>/static/images/diem-phung-thi.png</t>
-        </is>
+        <v>16.4715813</v>
+      </c>
+      <c r="G44" t="n">
+        <v>107.5763379</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/ho-noi-kim-thuy.png</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tượng đài Phan Bội Châu</t>
+          <t>Hồ Sơn Thọ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tượng đài Phan Bội Châu là điểm đến lịch sử nổi bật, tôn vinh nhà yêu nước tại trung tâm thành phố Vinh, Nghệ An.</t>
+          <t>Hồ Sơn Thọ là điểm đến lý tưởng với cảnh sắc hữu tình, không khí trong lành, thích hợp dã ngoại và thư giãn cuối tuần.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>16.46715</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F45" t="n">
-        <v>107.5898061</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>/static/images/tuong-dai-phan-boi-chau.png</t>
-        </is>
+        <v>16.3515757</v>
+      </c>
+      <c r="G45" t="n">
+        <v>107.5882024</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/ho-son-tho.png</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nhà Lưu Niệm Nguyễn Tất Thành</t>
+          <t>Không gian Văn hoá Lục Bộ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nhà lưu niệm thời niên thiếu của Chủ tịch Hồ Chí Minh tại làng Dương Nỗ, xã Phú Dương, TP. Huế. Nơi đây Bác Hồ (Nguyễn Sinh Cung) cùng cha và anh trai sinh sống từ năm 1898-1900. Di tích quốc gia đặc biệt được công nhận năm 2020.</t>
+          <t>Không gian Văn hoá Lục Bộ tái hiện sinh động lịch sử, văn hóa và ẩm thực đặc sắc của vùng đất Nam Bộ xưa.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>16.4891</v>
-      </c>
       <c r="F46" t="n">
-        <v>107.6534</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>/static/images/nha-luu-niem-nguyen-tat-thanh.png</t>
-        </is>
+        <v>16.4729593</v>
+      </c>
+      <c r="G46" t="n">
+        <v>107.5807931</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/khong-gian-van-hoa-luc-bo.png</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Đài Tưởng Niệm Tổ Quốc Ghi Công</t>
+          <t>Kỳ Đài</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Đài Tưởng Niệm Tổ Quốc Ghi Công là nơi trang nghiêm tưởng nhớ các anh hùng liệt sĩ đã hy sinh vì độc lập, tự do của Tổ quốc.</t>
+          <t>Kỳ Đài Huế là biểu tượng lịch sử nổi bật, nơi lưu giữ dấu ấn triều Nguyễn và thu hút du khách với kiến trúc cổ kính giữa lòng cố đô.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>16.3962863</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>107.5887</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>/static/images/dai-tuong-niem-to-quoc-ghi-cong.png</t>
-        </is>
+        <v>16.4663574</v>
+      </c>
+      <c r="G47" t="n">
+        <v>107.5802462</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/ky-dai.png</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cửu Vị Thần Công</t>
+          <t>Liễn làng Chuồn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cửu Vị Thần Công là bộ súng thần công nổi tiếng, biểu tượng lịch sử oai hùng tại Đại Nội Huế, thu hút du khách tham quan và tìm hiểu.</t>
+          <t>Liễn làng Chuồn nổi bật với nghệ thuật thư pháp truyền thống, phản ánh nét đẹp văn hóa và lịch sử đặc sắc của làng quê xứ Huế.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>16.4679198</v>
-      </c>
       <c r="F48" t="n">
-        <v>107.5812344</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>/static/images/cuu-vi-than-cong.png</t>
-        </is>
+        <v>16.5073733</v>
+      </c>
+      <c r="G48" t="n">
+        <v>107.6357846</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lien-lang-chuon.png</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bắc Khuyết Đài</t>
+          <t>Làng Hương Thủy Xuân</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bắc Khuyết Đài: điểm check-in nổi tiếng với kiến trúc độc đáo, view biển tuyệt đẹp và không gian yên bình giữa lòng Đà Nẵng.</t>
+          <t>Làng Hương Thủy Xuân nổi tiếng với nghề làm hương truyền thống, sắc màu rực rỡ, thu hút du khách khám phá văn hóa Huế.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>16.4719956</v>
-      </c>
       <c r="F49" t="n">
-        <v>107.5758125</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>/static/images/bac-khuyet-dai.png</t>
-        </is>
+        <v>16.43554</v>
+      </c>
+      <c r="G49" t="n">
+        <v>107.56227</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-huong-thuy-xuan.png</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bối Lăng</t>
+          <t>Làng mây tre đan Bao La</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bối Lăng là quần thể lăng mộ cổ kính, yên bình giữa rừng thông, lưu giữ dấu ấn triều đại nhà Lý tại Bắc Ninh.</t>
+          <t>Làng mây tre đan Bao La nổi tiếng với nghề thủ công truyền thống, sản phẩm tinh xảo và không gian làng quê yên bình, thu hút du khách trải nghiệm.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>16.4342482</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>107.5666428</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>/static/images/boi-lang.png</t>
-        </is>
+        <v>16.5394551</v>
+      </c>
+      <c r="G50" t="n">
+        <v>107.4709349</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-may-tre-dan-bao-la.png</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cầu Chợ Dinh</t>
+          <t>Làng nghề hoa giấy Thanh Tiên</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cầu Chợ Dinh bắc qua sông Nhật Lệ, là điểm check-in nổi bật với kiến trúc độc đáo và khung cảnh thơ mộng giữa lòng thành phố Đồng Hới.</t>
+          <t>Làng nghề hoa giấy Thanh Tiên nổi tiếng với những bông hoa giấy rực rỡ, lưu giữ nét đẹp truyền thống xứ Huế.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>16.4929675</v>
-      </c>
       <c r="F51" t="n">
-        <v>107.5924182</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>/static/images/cau-cho-dinh.png</t>
-        </is>
+        <v>16.5053321</v>
+      </c>
+      <c r="G51" t="n">
+        <v>107.5785503</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-nghe-hoa-giay-thanh-tien.png</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cầu Tam Giang</t>
+          <t>Làng nghề sơn mài thếp vàng Tiên Nộn</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cầu Tam Giang nổi bật giữa thiên nhiên thơ mộng, là điểm check-in lý tưởng ngắm bình minh và hoàng hôn trên phá Tam Giang.</t>
+          <t>Làng nghề sơn mài thếp vàng Tiên Nộn nổi tiếng với những sản phẩm thủ công tinh xảo, mang đậm nét văn hóa truyền thống Việt Nam.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>16.5821907</v>
-      </c>
       <c r="F52" t="n">
-        <v>107.5885002</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>/static/images/cau-tam-giang.png</t>
-        </is>
+        <v>16.4983321</v>
+      </c>
+      <c r="G52" t="n">
+        <v>107.5798678</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-nghe-son-mai-thep-vang-tien-non.png</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cầu Vĩ Dạ</t>
+          <t>Làng rèn Hiền Lương</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cầu Vĩ Dạ bắc qua sông An Cựu, nổi bật với vẻ đẹp thơ mộng, gắn liền thi ca và ký ức xứ Huế.</t>
+          <t>Làng rèn Hiền Lương nổi tiếng với nghề rèn truyền thống lâu đời, thu hút du khách bởi âm vang búa đe và sản phẩm tinh xảo.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>16.4714657</v>
-      </c>
       <c r="F53" t="n">
-        <v>107.5997497</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>/static/images/cau-vi-da.png</t>
-        </is>
+        <v>16.5582703</v>
+      </c>
+      <c r="G53" t="n">
+        <v>107.4691259</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-ren-hien-luong.png</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cầu Thủy Vân</t>
+          <t>Làng tránh Sình</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cầu Thủy Vân nổi bật với kiến trúc hiện đại, là điểm check-in lý tưởng giữa thiên nhiên thơ mộng và dòng sông êm đềm.</t>
+          <t>Làng Tranh Sình nổi tiếng với tranh dân gian truyền thống, không khí yên bình và nét văn hóa đặc sắc ven sông Hương.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>16.4824922</v>
-      </c>
       <c r="F54" t="n">
-        <v>107.6040878</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>/static/images/cau-thuy-van.png</t>
-        </is>
+        <v>16.5217578</v>
+      </c>
+      <c r="G54" t="n">
+        <v>107.5774757</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-tranh-sinh.png</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cầu Vân Dương</t>
+          <t>Lăng Dục Đức</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cầu Vân Dương nổi bật với kiến trúc hiện đại, nối liền hai bờ sông, là điểm check-in lý tưởng khi đến Quảng Trị.</t>
+          <t>Lăng Dục Đức là nơi yên nghỉ của vua Dục Đức, mang nét kiến trúc cổ kính và không gian thanh bình giữa lòng Huế.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>16.4741464</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F55" t="n">
-        <v>107.6078971</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>/static/images/cau-van-duong.png</t>
-        </is>
+        <v>16.4510937</v>
+      </c>
+      <c r="G55" t="n">
+        <v>107.5931525</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-duc-duc.png</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cầu Châu Sơn</t>
+          <t>Lăng Gia Long</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cầu Châu Sơn nổi bật với kiến trúc độc đáo, bắc qua sông Đáy, là điểm check-in hấp dẫn tại thành phố Phủ Lý, Hà Nam.</t>
+          <t>Lăng Gia Long là quần thể lăng tẩm uy nghi giữa núi rừng, hòa quyện thiên nhiên và kiến trúc độc đáo của triều Nguyễn.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>16.4183309</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F56" t="n">
-        <v>107.6536678</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>/static/images/cau-chau-son.png</t>
-        </is>
+        <v>16.36197</v>
+      </c>
+      <c r="G56" t="n">
+        <v>107.59694</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-gia-long.png</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tượng Đại Tướng Nguyễn Chí Thanh</t>
+          <t>Lăng Khải Định</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tượng Đại Tướng Nguyễn Chí Thanh uy nghi, là điểm đến ý nghĩa để tìm hiểu lịch sử và tưởng nhớ vị tướng tài ba của dân tộc.</t>
+          <t>Lăng Khải Định là công trình lăng tẩm độc đáo, kết hợp kiến trúc Đông Tây tinh xảo giữa núi non thơ mộng xứ Huế.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>16.5740947</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>107.5094706</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>/static/images/tuong-ai-tuong-nguyen-chi-thanh.png</t>
-        </is>
+        <v>16.3989</v>
+      </c>
+      <c r="G57" t="n">
+        <v>107.59029</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-khai-dinh.png</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Đại Cung Môn</t>
+          <t>Lăng Minh Mạng</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Đại Cung Môn là cổng chính uy nghi, biểu tượng lịch sử nổi bật của Hoàng thành Huế, thu hút du khách bởi kiến trúc độc đáo và giá trị văn hóa.</t>
+          <t>Lăng Minh Mạng là công trình kiến trúc uy nghi, hòa quyện thiên nhiên và nghệ thuật, nằm giữa không gian xanh mát của cố đô Huế.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>16.4691166</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F58" t="n">
-        <v>107.5780681</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>/static/images/ai-cung-mon.png</t>
-        </is>
+        <v>16.38748</v>
+      </c>
+      <c r="G58" t="n">
+        <v>107.57025</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-minh-mang.png</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tượng đài vua Quang Trung</t>
+          <t>Lăng Tự Đức</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tượng đài vua Quang Trung uy nghi, sừng sững giữa thành phố, là điểm đến lịch sử hấp dẫn du khách khi ghé thăm Quy Nhơn.</t>
+          <t>Lăng Tự Đức là quần thể lăng tẩm thơ mộng, hòa quyện giữa kiến trúc tinh tế và thiên nhiên hữu tình tại cố đô Huế.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>16.4420037</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Lăng tẩm</t>
+        </is>
       </c>
       <c r="F59" t="n">
-        <v>107.5914458</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>/static/images/tuong-ai-vua-quang-trung.png</t>
-        </is>
+        <v>16.43299</v>
+      </c>
+      <c r="G59" t="n">
+        <v>107.56644</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/lang-tu-duc.png</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Đàn Xã Tắc</t>
+          <t>Nem Lụi Bà Tý</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Đàn Xã Tắc là di tích lịch sử linh thiêng, nơi triều đình xưa tế lễ cầu cho quốc thái dân an tại Huế.</t>
+          <t>Nem Lụi Bà Tý thơm ngon, đậm vị, nướng than hồng, ăn kèm rau sống và nước chấm đặc biệt, là trải nghiệm ẩm thực Huế khó quên.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Di tích</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>16.4650415</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ẩm thực</t>
+        </is>
       </c>
       <c r="F60" t="n">
-        <v>107.5712089</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>/static/images/an-xa-tac.png</t>
-        </is>
+        <v>16.48003</v>
+      </c>
+      <c r="G60" t="n">
+        <v>107.58339</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nem-lui-ba-ty.png</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hồ Sơn Thọ</t>
+          <t>Ngọ Môn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hồ Sơn Thọ là điểm đến lý tưởng với cảnh sắc hữu tình, không khí trong lành, thích hợp dã ngoại và thư giãn cuối tuần.</t>
+          <t>Ngọ Môn là cổng chính hoành tráng của Hoàng thành Huế, nổi bật với kiến trúc cổ kính và giá trị lịch sử đặc sắc.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>16.3515757</v>
-      </c>
       <c r="F61" t="n">
-        <v>107.5882024</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>/static/images/ho-son-tho.png</t>
-        </is>
+        <v>16.4676824</v>
+      </c>
+      <c r="G61" t="n">
+        <v>107.5791834</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/ngo-mon.png</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Làng mây tre đan Bao La</t>
+          <t>Nhà Lưu Niệm Nguyễn Tất Thành</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Làng mây tre đan Bao La nổi tiếng với nghề thủ công truyền thống, sản phẩm tinh xảo và không gian làng quê yên bình, thu hút du khách trải nghiệm.</t>
+          <t>Nhà lưu niệm thời niên thiếu của Chủ tịch Hồ Chí Minh tại làng Dương Nỗ, xã Phú Dương, TP. Huế. Nơi đây Bác Hồ (Nguyễn Sinh Cung) cùng cha và anh trai sinh sống từ năm 1898-1900. Di tích quốc gia đặc biệt được công nhận năm 2020.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>16.5394551</v>
-      </c>
       <c r="F62" t="n">
-        <v>107.4709349</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>/static/images/lang-may-tre-an-bao-la.png</t>
-        </is>
+        <v>16.4891</v>
+      </c>
+      <c r="G62" t="n">
+        <v>107.6534</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nha-luu-niem-nguyen-tat-thanh.png</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Đúc đồng Dương Xuân</t>
+          <t>Nhà Thờ Phủ Cam</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Đúc đồng Dương Xuân nổi tiếng với nghệ thuật chế tác tinh xảo, lưu giữ nét truyền thống và văn hóa đặc sắc của làng nghề Huế.</t>
+          <t>Nhà Thờ Phủ Cam nổi bật với kiến trúc độc đáo, không gian yên bình, là điểm đến tâm linh và check-in hấp dẫn tại Huế.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>16.4532498</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F63" t="n">
-        <v>107.5632941</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>/static/images/uc-ong-duong-xuan.png</t>
-        </is>
+        <v>16.4528612</v>
+      </c>
+      <c r="G63" t="n">
+        <v>107.5876632</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nha-tho-phu-cam.png</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Làng tránh Sình</t>
+          <t>Nhà Trưng Bày Nông Cụ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Làng Tranh Sình nổi tiếng với tranh dân gian truyền thống, không khí yên bình và nét văn hóa đặc sắc ven sông Hương.</t>
+          <t>Nhà Trưng Bày Nông Cụ giới thiệu các dụng cụ truyền thống, tái hiện sinh động đời sống lao động của người nông dân Việt Nam xưa.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>16.5217578</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>107.5774757</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>/static/images/lang-tranh-sinh.png</t>
-        </is>
+        <v>16.4667817</v>
+      </c>
+      <c r="G64" t="n">
+        <v>107.6421227</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nha-trung-bay-nong-cu.png</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Làng rèn Hiền Lương</t>
+          <t>Nhà vườn An Hiên</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Làng rèn Hiền Lương nổi tiếng với nghề rèn truyền thống lâu đời, thu hút du khách bởi âm vang búa đe và sản phẩm tinh xảo.</t>
+          <t>Nhà vườn An Hiên là không gian xanh mát, yên bình, mang đậm nét kiến trúc và văn hóa truyền thống xứ Huế.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>16.5582703</v>
-      </c>
       <c r="F65" t="n">
-        <v>107.4691259</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>/static/images/lang-ren-hien-luong.png</t>
-        </is>
+        <v>16.45532</v>
+      </c>
+      <c r="G65" t="n">
+        <v>107.55378</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nha-vuon-an-hien.png</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Làng nghề sơn mài thếp vàng Tiên Nộn</t>
+          <t>Núi Ngự Bình</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Làng nghề sơn mài thếp vàng Tiên Nộn nổi tiếng với những sản phẩm thủ công tinh xảo, mang đậm nét văn hóa truyền thống Việt Nam.</t>
+          <t>Núi Ngự Bình là biểu tượng thiên nhiên thơ mộng của Huế, nổi bật với dáng núi uy nghi và khung cảnh yên bình bên dòng sông Hương.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>16.4983321</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F66" t="n">
-        <v>107.5798678</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>/static/images/lang-nghe-son-mai-thep-vang-tien-non.png</t>
-        </is>
+        <v>16.44168</v>
+      </c>
+      <c r="G66" t="n">
+        <v>107.5961</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/nui-ngu-binh.png</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Làng nghề hoa giấy Thanh Tiên</t>
+          <t>Phá Tam Giang</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Làng nghề hoa giấy Thanh Tiên nổi tiếng với những bông hoa giấy rực rỡ, lưu giữ nét đẹp truyền thống xứ Huế.</t>
+          <t>Phá Tam Giang là đầm nước lợ lớn nhất Đông Nam Á, nổi bật với cảnh hoàng hôn tuyệt đẹp và trải nghiệm chèo thuyền độc đáo.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>16.5053321</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F67" t="n">
-        <v>107.5785503</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>/static/images/lang-nghe-hoa-giay-thanh-tien.png</t>
-        </is>
+        <v>16.59788</v>
+      </c>
+      <c r="G67" t="n">
+        <v>107.54309</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/pha-tam-giang.png</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Liễn làng Chuồn</t>
+          <t>Phủ Nội Vụ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Liễn làng Chuồn nổi bật với nghệ thuật thư pháp truyền thống, phản ánh nét đẹp văn hóa và lịch sử đặc sắc của làng quê xứ Huế.</t>
+          <t>Phủ Nội Vụ là di tích lịch sử nổi bật trong Hoàng thành Thăng Long, nổi bật với kiến trúc cổ kính và giá trị văn hóa đặc sắc.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>16.5073733</v>
-      </c>
       <c r="F68" t="n">
-        <v>107.6357846</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>/static/images/lien-lang-chuon.png</t>
-        </is>
+        <v>16.4706162</v>
+      </c>
+      <c r="G68" t="n">
+        <v>107.5797647</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/phu-noi-vu.png</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Công viên Hồ Thủy Tiên</t>
+          <t>Quan Tượng Đài (Nam Đài)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Công viên Hồ Thủy Tiên là điểm check-in huyền bí với hồ nước, rừng cây và rồng khổng lồ bỏ hoang giữa lòng Huế.</t>
+          <t>Quan Tượng Đài (Nam Đài) là điểm ngắm cảnh lý tưởng, nơi du khách chiêm ngưỡng toàn cảnh thành phố Huế và sông Hương thơ mộng.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>16.4112974</v>
-      </c>
       <c r="F69" t="n">
-        <v>107.5738937</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>/static/images/cong-vien-ho-thuy-tien.png</t>
-        </is>
+        <v>16.4621728</v>
+      </c>
+      <c r="G69" t="n">
+        <v>107.5707363</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/quan-tuong-dai-nam-dai.png</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quan Tượng Đài (Nam Đài)</t>
+          <t>Quốc Tử Giám</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Quan Tượng Đài (Nam Đài) là điểm ngắm cảnh lý tưởng, nơi du khách chiêm ngưỡng toàn cảnh thành phố Huế và sông Hương thơ mộng.</t>
+          <t>Quốc Tử Giám là trường đại học đầu tiên của Việt Nam, nổi bật với kiến trúc cổ kính và không gian yên bình giữa lòng Hà Nội.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>16.4621728</v>
-      </c>
       <c r="F70" t="n">
-        <v>107.5707363</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>/static/images/quan-tuong-ai-nam-ai.png</t>
-        </is>
+        <v>16.4705977</v>
+      </c>
+      <c r="G70" t="n">
+        <v>107.5824866</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/quoc-tu-giam.png</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bi Đình</t>
+          <t>Rừng ngập mặn Rú Chá</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bi Đình là điểm dừng chân yên bình giữa thiên nhiên, nổi bật với kiến trúc cổ kính và không gian thanh tịnh.</t>
+          <t>Khám phá Rú Chá - rừng ngập mặn nguyên sinh độc đáo, hòa mình vào thiên nhiên hoang sơ và tận hưởng không khí trong lành ven phá Tam Giang.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>16.4331868</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>107.5653998</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>/static/images/bi-inh.png</t>
-        </is>
+        <v>16.55748</v>
+      </c>
+      <c r="G71" t="n">
+        <v>107.61144</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/rung-ngap-man-ru-cha.png</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lăng Dục Đức</t>
+          <t>Suối Voi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lăng Dục Đức là nơi yên nghỉ của vua Dục Đức, mang nét kiến trúc cổ kính và không gian thanh bình giữa lòng Huế.</t>
+          <t>Suối Voi là điểm đến hoang sơ, nước trong xanh, cảnh sắc thiên nhiên tuyệt đẹp, lý tưởng để thư giãn và khám phá giữa núi rừng Huế.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lăng tẩm</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>16.4510937</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F72" t="n">
-        <v>107.5931525</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>/static/images/lang-duc-uc.png</t>
-        </is>
+        <v>16.24387</v>
+      </c>
+      <c r="G72" t="n">
+        <v>107.98943</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/suoi-voi.png</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Điện Biên Phủ</t>
+          <t>Sông Hương</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Điện Biên Phủ - điểm đến lịch sử hào hùng, cảnh sắc núi non hùng vĩ và văn hóa dân tộc đặc sắc.</t>
+          <t>Sông Hương thơ mộng uốn lượn giữa lòng Huế, phản chiếu vẻ đẹp trầm mặc và lãng mạn của cố đô.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>16.4566552</v>
-      </c>
       <c r="F73" t="n">
-        <v>107.5809463</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>/static/images/ien-bien-phu.png</t>
-        </is>
+        <v>16.47021</v>
+      </c>
+      <c r="G73" t="n">
+        <v>107.59024</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/song-huong.png</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cầu Ga</t>
+          <t>Thái Miếu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cầu Ga nổi bật với kiến trúc độc đáo, là điểm check-in lý tưởng giữa thiên nhiên thơ mộng của Đà Lạt.</t>
+          <t>Thái Miếu là di tích linh thiêng, nơi thờ các vua chúa triều Nguyễn, nổi bật với kiến trúc cổ kính giữa lòng kinh thành Huế.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>16.4572126</v>
-      </c>
       <c r="F74" t="n">
-        <v>107.5788716</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>/static/images/cau-ga.png</t>
-        </is>
+        <v>16.4699025</v>
+      </c>
+      <c r="G74" t="n">
+        <v>107.5803251</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/thai-mieu.png</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trung tâm Nghệ thuật Điềm Phùng Thị</t>
+          <t>Thương Bạc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Trung tâm Nghệ thuật Điềm Phùng Thị là không gian trưng bày các tác phẩm điêu khắc độc đáo, tôn vinh nghệ sĩ nổi tiếng của Việt Nam.</t>
+          <t>Thương Bạc là khu phố sầm uất ở Huế, nổi bật với kiến trúc cổ kính và không khí nhộn nhịp, thu hút du khách khám phá văn hóa địa phương.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>16.4669715</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F75" t="n">
-        <v>107.5895601</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>/static/images/trung-tam-nghe-thuat-iem-phung-thi.png</t>
-        </is>
+        <v>16.4680333</v>
+      </c>
+      <c r="G75" t="n">
+        <v>107.5855685</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/thuong-bac.png</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Trung tâm Thanh thiếu nhi Huế</t>
+          <t>Triệu Miếu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Trung tâm Thanh thiếu nhi Huế là điểm vui chơi, học tập sôi động dành cho giới trẻ, với nhiều hoạt động bổ ích và không gian hiện đại.</t>
+          <t>Triệu Miếu là ngôi đền cổ kính ở Huế, thờ các vua triều Nguyễn, nổi bật với kiến trúc truyền thống và không gian yên bình.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>16.4592467</v>
-      </c>
       <c r="F76" t="n">
-        <v>107.5822457</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>/static/images/trung-tam-thanh-thieu-nhi-hue.png</t>
-        </is>
+        <v>16.4701991</v>
+      </c>
+      <c r="G76" t="n">
+        <v>107.5800933</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/trieu-mieu.png</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ngọ Môn</t>
+          <t>Trung tâm Nghệ thuật Điềm Phùng Thị</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ngọ Môn là cổng chính hoành tráng của Hoàng thành Huế, nổi bật với kiến trúc cổ kính và giá trị lịch sử đặc sắc.</t>
+          <t>Trung tâm Nghệ thuật Điềm Phùng Thị là không gian trưng bày các tác phẩm điêu khắc độc đáo, tôn vinh nghệ sĩ nổi tiếng của Việt Nam.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>16.4676824</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F77" t="n">
-        <v>107.5791834</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>/static/images/ngo-mon.png</t>
-        </is>
+        <v>16.4669715</v>
+      </c>
+      <c r="G77" t="n">
+        <v>107.5895601</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/trung-tam-nghe-thuat-diem-phung-thi.png</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Duyệt Thị Đường</t>
+          <t>Trung tâm Thanh thiếu nhi Huế</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Duyệt Thị Đường là nhà hát cổ kính trong Hoàng thành Thăng Long, nơi lưu giữ nghệ thuật múa rối nước truyền thống Việt Nam.</t>
+          <t>Trung tâm Thanh thiếu nhi Huế là điểm vui chơi, học tập sôi động dành cho giới trẻ, với nhiều hoạt động bổ ích và không gian hiện đại.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E78" t="n">
-        <v>16.4703036</v>
-      </c>
       <c r="F78" t="n">
-        <v>107.5784839</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>/static/images/duyet-thi-uong.png</t>
-        </is>
+        <v>16.4592467</v>
+      </c>
+      <c r="G78" t="n">
+        <v>107.5822457</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/trung-tam-thanh-thieu-nhi-hue.png</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hưng Tổ Miếu</t>
+          <t>Trường An Môn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hưng Tổ Miếu là di tích lịch sử linh thiêng, nơi thờ các vị tổ nhà Nguyễn, thu hút du khách bởi kiến trúc cổ kính và không gian yên bình.</t>
+          <t>Trường An Môn là cổng thành cổ nổi tiếng, biểu tượng lịch sử và văn hóa đặc sắc giữa lòng Bắc Kinh.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E79" t="n">
-        <v>16.4675459</v>
-      </c>
       <c r="F79" t="n">
-        <v>107.5764287</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>/static/images/hung-to-mieu.png</t>
-        </is>
+        <v>16.470085</v>
+      </c>
+      <c r="G79" t="n">
+        <v>107.5752197</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/truong-an-mon.png</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Thái Miếu</t>
+          <t>Trường THPT chuyên Quốc Học Huế</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thái Miếu là di tích linh thiêng, nơi thờ các vua chúa triều Nguyễn, nổi bật với kiến trúc cổ kính giữa lòng kinh thành Huế.</t>
+          <t>Trường THPT chuyên Quốc Học Huế nổi bật với kiến trúc cổ kính, không gian xanh mát và bề dày lịch sử hơn 125 năm.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E80" t="n">
-        <v>16.4699025</v>
-      </c>
       <c r="F80" t="n">
-        <v>107.5803251</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>/static/images/thai-mieu.png</t>
-        </is>
+        <v>16.46008</v>
+      </c>
+      <c r="G80" t="n">
+        <v>107.58335</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/truong-thpt-chuyen-quoc-hoc-hue.png</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Triệu Miếu</t>
+          <t>Tây Khuyết Đài</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Triệu Miếu là ngôi đền cổ kính ở Huế, thờ các vua triều Nguyễn, nổi bật với kiến trúc truyền thống và không gian yên bình.</t>
+          <t>Tây Khuyết Đài Huế là điểm ngắm hoàng hôn tuyệt đẹp, lưu giữ dấu ấn lịch sử triều Nguyễn giữa lòng kinh thành cổ kính.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E81" t="n">
-        <v>16.4701991</v>
-      </c>
       <c r="F81" t="n">
-        <v>107.5800933</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>/static/images/trieu-mieu.png</t>
-        </is>
+        <v>16.468038</v>
+      </c>
+      <c r="G81" t="n">
+        <v>107.5750678</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tay-khuyet-dai.png</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Phủ Nội Vụ</t>
+          <t>Tượng Đại Tướng Nguyễn Chí Thanh</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phủ Nội Vụ là di tích lịch sử nổi bật trong Hoàng thành Thăng Long, nổi bật với kiến trúc cổ kính và giá trị văn hóa đặc sắc.</t>
+          <t>Tượng Đại Tướng Nguyễn Chí Thanh uy nghi, là điểm đến ý nghĩa để tìm hiểu lịch sử và tưởng nhớ vị tướng tài ba của dân tộc.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>16.4706162</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F82" t="n">
-        <v>107.5797647</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>/static/images/phu-noi-vu.png</t>
-        </is>
+        <v>16.5740947</v>
+      </c>
+      <c r="G82" t="n">
+        <v>107.5094706</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tuong-dai-tuong-nguyen-chi-thanh.png</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cung Diên Thọ</t>
+          <t>Tượng đài Phan Bội Châu</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cung Diên Thọ là nơi nghỉ ngơi của Hoàng thái hậu, nổi bật với kiến trúc cổ kính và không gian yên bình trong Đại Nội Huế.</t>
+          <t>Tượng đài Phan Bội Châu là điểm đến lịch sử nổi bật, tôn vinh nhà yêu nước tại trung tâm thành phố Vinh, Nghệ An.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>16.4688916</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F83" t="n">
-        <v>107.5754008</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>/static/images/cung-dien-tho.png</t>
-        </is>
+        <v>16.46715</v>
+      </c>
+      <c r="G83" t="n">
+        <v>107.5898061</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tuong-dai-phan-boi-chau.png</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cung Trường Sanh</t>
+          <t>Tượng đài Quan Thế Âm Bồ Tát</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cung Trường Sanh là công trình cổ kính, yên bình giữa Đại Nội Huế, nổi bật với kiến trúc độc đáo và không gian xanh mát.</t>
+          <t>Tượng đài Quan Thế Âm Bồ Tát uy nghi giữa thiên nhiên, là điểm đến tâm linh nổi bật thu hút du khách thập phương.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>16.4697182</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F84" t="n">
-        <v>107.5746783</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>/static/images/cung-truong-sanh.png</t>
-        </is>
+        <v>16.3920792</v>
+      </c>
+      <c r="G84" t="n">
+        <v>107.5841879</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tuong-dai-quan-the-am-bo-tat.png</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kỳ Đài</t>
+          <t>Tượng đài vua Quang Trung</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kỳ Đài Huế là biểu tượng lịch sử nổi bật, nơi lưu giữ dấu ấn triều Nguyễn và thu hút du khách với kiến trúc cổ kính giữa lòng cố đô.</t>
+          <t>Tượng đài vua Quang Trung uy nghi, sừng sững giữa thành phố, là điểm đến lịch sử hấp dẫn du khách khi ghé thăm Quy Nhơn.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>16.4663574</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F85" t="n">
-        <v>107.5802462</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>/static/images/ky-ai.png</t>
-        </is>
+        <v>16.4420037</v>
+      </c>
+      <c r="G85" t="n">
+        <v>107.5914458</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tuong-dai-vua-quang-trung.png</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Thương Bạc</t>
+          <t>Tử Cấm Thành</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thương Bạc là khu phố sầm uất ở Huế, nổi bật với kiến trúc cổ kính và không khí nhộn nhịp, thu hút du khách khám phá văn hóa địa phương.</t>
+          <t>Tử Cấm Thành là cung điện cổ kính, biểu tượng quyền lực triều đại Minh - Thanh, nổi bật với kiến trúc nguy nga giữa lòng Bắc Kinh.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>16.4680333</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F86" t="n">
-        <v>107.5855685</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>/static/images/thuong-bac.png</t>
-        </is>
+        <v>16.4694914</v>
+      </c>
+      <c r="G86" t="n">
+        <v>107.577755</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/tu-cam-thanh.png</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bảo tàng Hồ Chí Minh</t>
+          <t>Viện Cơ Mật - Tam Toà</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bảo tàng Hồ Chí Minh lưu giữ nhiều hiện vật, tư liệu quý về cuộc đời và sự nghiệp của Chủ tịch Hồ Chí Minh, thu hút đông đảo du khách tham quan.</t>
+          <t>Viện Cơ Mật - Tam Toà là di tích lịch sử triều Nguyễn, nổi bật với kiến trúc cổ kính và giá trị văn hóa đặc sắc tại Huế.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Bảo tàng</t>
         </is>
       </c>
-      <c r="E87" t="n">
-        <v>16.4596249</v>
-      </c>
       <c r="F87" t="n">
-        <v>107.5811082</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>/static/images/bao-tang-ho-chi-minh.png</t>
-        </is>
+        <v>16.4719593</v>
+      </c>
+      <c r="G87" t="n">
+        <v>107.583647</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/vien-co-mat-tam-toa.png</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nhà Trưng Bày Nông Cụ</t>
+          <t>Văn Thánh Huế</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nhà Trưng Bày Nông Cụ giới thiệu các dụng cụ truyền thống, tái hiện sinh động đời sống lao động của người nông dân Việt Nam xưa.</t>
+          <t>Văn Thánh Huế là di tích lịch sử nổi bật, lưu giữ giá trị văn hóa và truyền thống hiếu học của vùng đất cố đô.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>16.4667817</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F88" t="n">
-        <v>107.6421227</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>/static/images/nha-trung-bay-nong-cu.png</t>
-        </is>
+        <v>16.452965</v>
+      </c>
+      <c r="G88" t="n">
+        <v>107.538902</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/van-thanh-hue.png</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Đông Khuyết Đài</t>
+          <t>Vườn Quốc gia Bạch Mã</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Đông Khuyết Đài là điểm đến lịch sử nổi bật với kiến trúc cổ kính, không gian yên bình và tầm nhìn tuyệt đẹp tại kinh thành Huế.</t>
+          <t>Vườn Quốc gia Bạch Mã nổi bật với rừng nguyên sinh, thác nước hùng vĩ và hệ động thực vật đa dạng, lý tưởng cho du lịch sinh thái.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>16.471596</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F89" t="n">
-        <v>107.5800406</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>/static/images/ong-khuyet-ai.png</t>
-        </is>
+        <v>16.2165</v>
+      </c>
+      <c r="G89" t="n">
+        <v>107.89365</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/vuon-quoc-gia-bach-ma.png</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Quốc Tử Giám</t>
+          <t>Điềm Phùng Thị</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Quốc Tử Giám là trường đại học đầu tiên của Việt Nam, nổi bật với kiến trúc cổ kính và không gian yên bình giữa lòng Hà Nội.</t>
+          <t>Khám phá không gian nghệ thuật độc đáo tại Bảo tàng Điềm Phùng Thị, nơi lưu giữ tinh hoa điêu khắc Việt Nam hiện đại.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>16.4705977</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Bảo tàng</t>
+        </is>
       </c>
       <c r="F90" t="n">
-        <v>107.5824866</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>/static/images/quoc-tu-giam.png</t>
-        </is>
+        <v>16.4578346</v>
+      </c>
+      <c r="G90" t="n">
+        <v>107.5842155</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/diem-phung-thi.png</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Điện Thái Hòa</t>
+          <t>Điện Biên Phủ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Điện Thái Hòa là công trình kiến trúc nổi bật, nơi diễn ra các nghi lễ quan trọng của triều đình nhà Nguyễn tại Hoàng thành Huế.</t>
+          <t>Điện Biên Phủ - điểm đến lịch sử hào hùng, cảnh sắc núi non hùng vĩ và văn hóa dân tộc đặc sắc.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E91" t="n">
-        <v>16.4687434</v>
-      </c>
       <c r="F91" t="n">
-        <v>107.5783867</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>/static/images/dien-thai-hoa.png</t>
-        </is>
+        <v>16.4566552</v>
+      </c>
+      <c r="G91" t="n">
+        <v>107.5809463</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dien-bien-phu.png</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tây Khuyết Đài</t>
+          <t>Điện Hòn Chén</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tây Khuyết Đài Huế là điểm ngắm hoàng hôn tuyệt đẹp, lưu giữ dấu ấn lịch sử triều Nguyễn giữa lòng kinh thành cổ kính.</t>
+          <t>Điện Hòn Chén là điểm du lịch tâm linh nổi tiếng bên sông Hương, thu hút du khách bởi kiến trúc độc đáo và không gian linh thiêng.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>16.468038</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Tâm linh</t>
+        </is>
       </c>
       <c r="F92" t="n">
-        <v>107.5750678</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>/static/images/tay-khuyet-ai.png</t>
-        </is>
+        <v>16.42195</v>
+      </c>
+      <c r="G92" t="n">
+        <v>107.56296</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dien-hon-chen.png</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trường An Môn</t>
+          <t>Điện Thái Hòa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Trường An Môn là cổng thành cổ nổi tiếng, biểu tượng lịch sử và văn hóa đặc sắc giữa lòng Bắc Kinh.</t>
+          <t>Điện Thái Hòa là công trình kiến trúc nổi bật, nơi diễn ra các nghi lễ quan trọng của triều đình nhà Nguyễn tại Hoàng thành Huế.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Tham quan</t>
         </is>
       </c>
-      <c r="E93" t="n">
-        <v>16.470085</v>
-      </c>
       <c r="F93" t="n">
-        <v>107.5752197</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>/static/images/truong-an-mon.png</t>
-        </is>
+        <v>16.4687434</v>
+      </c>
+      <c r="G93" t="n">
+        <v>107.5783867</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dien-thai-hoa.png</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Di tích Nhà Lưu niệm Chủ tịch Hồ Chí Minh</t>
+          <t>Đàn Nam Giao</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Di tích Nhà Lưu niệm Chủ tịch Hồ Chí Minh là nơi lưu giữ kỷ vật, tái hiện cuộc sống giản dị của Bác tại quê hương.</t>
+          <t>Đàn Nam Giao là nơi triều Nguyễn tổ chức lễ tế trời linh thiêng, mang đậm dấu ấn văn hóa tâm linh cố đô Huế.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>16.4756171</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F94" t="n">
-        <v>107.5806219</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>/static/images/di-tich-nha-luu-niem-chu-tich-ho-chi-minh.png</t>
-        </is>
+        <v>16.4378</v>
+      </c>
+      <c r="G94" t="n">
+        <v>107.5827</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dan-nam-giao.png</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Viện Cơ Mật - Tam Toà</t>
+          <t>Đàn Xã Tắc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Viện Cơ Mật - Tam Toà là di tích lịch sử triều Nguyễn, nổi bật với kiến trúc cổ kính và giá trị văn hóa đặc sắc tại Huế.</t>
+          <t>Đàn Xã Tắc là di tích lịch sử linh thiêng, nơi triều đình xưa tế lễ cầu cho quốc thái dân an tại Huế.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>16.4719593</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F95" t="n">
-        <v>107.583647</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>/static/images/vien-co-mat-tam-toa.png</t>
-        </is>
+        <v>16.4650415</v>
+      </c>
+      <c r="G95" t="n">
+        <v>107.5712089</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dan-xa-tac.png</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bảo tàng Lịch sử Thừa Thiên Huế</t>
+          <t>Đông Khuyết Đài</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bảo tàng Lịch sử Thừa Thiên Huế lưu giữ nhiều hiện vật quý, tái hiện lịch sử và văn hóa đặc sắc của vùng đất cố đô.</t>
+          <t>Đông Khuyết Đài là điểm đến lịch sử nổi bật với kiến trúc cổ kính, không gian yên bình và tầm nhìn tuyệt đẹp tại kinh thành Huế.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>16.4698535</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F96" t="n">
-        <v>107.5825025</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>/static/images/bao-tang-lich-su-thua-thien-hue.png</t>
-        </is>
+        <v>16.471596</v>
+      </c>
+      <c r="G96" t="n">
+        <v>107.5800406</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dong-khuyet-ai.png</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bảo tàng Cổ vật Cung đình Huế</t>
+          <t>Đúc đồng Dương Xuân</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bảo tàng Cổ vật Cung đình Huế lưu giữ nhiều báu vật triều Nguyễn, phản ánh nét đẹp văn hóa cung đình xưa giữa không gian cổ kính.</t>
+          <t>Đúc đồng Dương Xuân nổi tiếng với nghệ thuật chế tác tinh xảo, lưu giữ nét truyền thống và văn hóa đặc sắc của làng nghề Huế.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Bảo tàng</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>16.4713073</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Tham quan</t>
+        </is>
       </c>
       <c r="F97" t="n">
-        <v>107.5819424</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>/static/images/bao-tang-co-vat-cung-inh-hue.png</t>
-        </is>
+        <v>16.4532498</v>
+      </c>
+      <c r="G97" t="n">
+        <v>107.5632941</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/duc-dong-duong-xuan.png</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Không gian Văn hoá Lục Bộ</t>
+          <t>Đại Cung Môn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Không gian Văn hoá Lục Bộ tái hiện sinh động lịch sử, văn hóa và ẩm thực đặc sắc của vùng đất Nam Bộ xưa.</t>
+          <t>Đại Cung Môn là cổng chính uy nghi, biểu tượng lịch sử nổi bật của Hoàng thành Huế, thu hút du khách bởi kiến trúc độc đáo và giá trị văn hóa.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>16.4729593</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Di tích</t>
+        </is>
       </c>
       <c r="F98" t="n">
-        <v>107.5807931</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>/static/images/khong-gian-van-hoa-luc-bo.png</t>
-        </is>
+        <v>16.4691166</v>
+      </c>
+      <c r="G98" t="n">
+        <v>107.5780681</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dai-cung-mon.png</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Chùa Diệu Đế</t>
+          <t>Đầm Lập An</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chùa Diệu Đế là ngôi chùa cổ kính bên sông Hương, nổi bật với kiến trúc độc đáo và không gian thanh tịnh giữa lòng Huế.</t>
+          <t>Đầm Lập An là viên ngọc xanh giữa lòng núi, nổi bật với mặt nước phẳng lặng và cảnh sắc thơ mộng, lý tưởng để thư giãn và chụp ảnh.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>16.4779515</v>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
       </c>
       <c r="F99" t="n">
-        <v>107.5875648</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>/static/images/chua-dieu-e.png</t>
-        </is>
+        <v>16.22142</v>
+      </c>
+      <c r="G99" t="n">
+        <v>108.06157</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Huế</t>
+          <t>/static/images/dam-lap-an.png</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>Đồi Vọng Cảnh</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Đồi Vọng Cảnh là điểm ngắm cảnh tuyệt đẹp, nơi du khách chiêm ngưỡng sông Hương và thành phố Huế từ trên cao.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Huế</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Thiên nhiên</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>16.42723</v>
+      </c>
+      <c r="G100" t="n">
+        <v>107.56493</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>/static/images/doi-vong-canh.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>user03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thùy Linh</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>123</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>user04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Đức Huy</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>123</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>123</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>123</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>user07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Phương Thảo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>123</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>123</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>user09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mai Lan</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>123</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>123</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>123</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>123</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>user13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bảo Ngọc</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>123</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>user14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>123</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>123</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>123</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>user17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kim Chi</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>123</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>123</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>123</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>123</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>user_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>location_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bãi biển Thuận An</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chợ An Cựu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hưng Tổ Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lăng Khải Định</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trường An Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>user01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Minh Anh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kỳ Đài</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Cầu Ga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Đông Khuyết Đài</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Triệu Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Quốc Tử Giám</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>user02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hoàng Long</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Không gian Văn hoá Lục Bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>user03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Thùy Linh</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bi Đình</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>user03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Thùy Linh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tượng đài vua Quang Trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>user03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thùy Linh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Cầu Trường Tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>user04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Đức Huy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Suối Voi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>user04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Đức Huy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Làng mây tre đan Bao La</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>user04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Đức Huy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Đồi Vọng Cảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>user04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Đức Huy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chợ Tây Lộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Núi Ngự Bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tượng đài Phan Bội Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Triệu Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hưng Tổ Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Trường An Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>user05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ngọc Hà</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chùa Huyền Không Sơn Thượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hưng Tổ Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hoàng Thành Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nhà Trưng Bày Nông Cụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chùa Thiên Mụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Làng tránh Sình</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Quốc Tử Giám</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>user06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quang Hải</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chợ Đông Ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>user07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Phương Thảo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Đồi Vọng Cảnh</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>user07</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Phương Thảo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chợ Tây Lộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>user07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Phương Thảo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Quốc Tử Giám</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tượng đài Phan Bội Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Làng mây tre đan Bao La</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ngọ Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Làng nghề hoa giấy Thanh Tiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Vườn Quốc gia Bạch Mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>user08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tuấn Kiệt</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Đầm Lập An</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>user09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mai Lan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ngọ Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>user09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mai Lan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cầu Chợ Dinh</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>user09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mai Lan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Trung tâm Nghệ thuật Điềm Phùng Thị</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>user09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mai Lan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chợ Xép</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Nhà Thờ Phủ Cam</t>
         </is>
       </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Triệu Miếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Làng nghề sơn mài thếp vàng Tiên Nộn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Quan Tượng Đài (Nam Đài)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>user10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Văn Nam</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chợ Xép</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ga Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Văn Thánh Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bảo tàng Cổ vật Cung đình Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Trung tâm Thanh thiếu nhi Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Trường An Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nhà vườn An Hiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>user11</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Thanh Tâm</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chè Hẻm Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ngọ Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tượng Đại Tướng Nguyễn Chí Thanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bãi biển Thuận An</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Làng mây tre đan Bao La</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Đàn Xã Tắc</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cầu Thủy Vân</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>user12</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hồng Nhung</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Suối Voi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>user13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Bảo Ngọc</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tượng đài Phan Bội Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>user13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Bảo Ngọc</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cầu Vĩ Dạ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>user13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bảo Ngọc</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Thương Bạc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>user14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chùa Diệu Đế</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>user14</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Lăng Gia Long</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>user14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tiến Đạt</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Điềm Phùng Thị</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cung An Định</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cầu Châu Sơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Điện Hòn Chén</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Trung tâm Nghệ thuật Điềm Phùng Thị</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cầu Gỗ Lim</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bảo tàng Cổ vật Cung đình Huế</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>user15</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Yến Nhi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chùa Huyền Không Sơn Thượng</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Công viên Hồ Thủy Tiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Đài Tưởng Niệm Tổ Quốc Ghi Công</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Nhà Trưng Bày Nông Cụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Đại Cung Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>user16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Công Vinh</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Chùa Từ Đàm</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>user17</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kim Chi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Chợ An Cựu</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>user17</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kim Chi</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cửu Vị Thần Công</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>user17</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kim Chi</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Làng Hương Thủy Xuân</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>user17</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kim Chi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Duyệt Thị Đường</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Đại Cung Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tây Khuyết Đài</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Làng nghề sơn mài thếp vàng Tiên Nộn</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Cầu Ga</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>user18</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Trung Hiếu</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Công viên Hồ Thủy Tiên</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chợ Tây Lộc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ngọ Môn</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chùa Từ Đàm</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Vườn Quốc gia Bạch Mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>user19</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ánh Dương</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Điện Biên Phủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cầu Tam Giang</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Bãi biển Lăng Cô</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chợ Đông Ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nhà Thờ Phủ Cam nổi bật với kiến trúc độc đáo, không gian yên bình, là điểm đến tâm linh và check-in hấp dẫn tại Huế.</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Tâm linh</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>16.4528612</v>
-      </c>
-      <c r="F100" t="n">
-        <v>107.5876632</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>/static/images/nha-tho-phu-cam.png</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Huế</t>
+          <t>Đồi Vọng Cảnh</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>100</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hồ Nội Kim Thủy</t>
+          <t>Hữu Phúc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hồ Nội Kim Thủy xanh biếc, yên bình giữa núi non, là điểm đến lý tưởng để thư giãn và tận hưởng không khí trong lành.</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Tham quan</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>16.4715813</v>
-      </c>
-      <c r="F101" t="n">
-        <v>107.5763379</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>/static/images/ho-noi-kim-thuy.png</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Huế</t>
+          <t>Lăng Dục Đức</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Đàn Nam Giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Điện Thái Hòa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>user20</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hữu Phúc</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Suối Voi</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Locations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Likes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Likes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>lng</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>image</t>
         </is>
@@ -3387,7 +3399,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tượng đài Phan Bội Châu là điểm đến lịch sử nổi bật, tôn vinh nhà yêu nước tại trung tâm thành phố Vinh, Nghệ An.</t>
+          <t>Khu lưu niệm Phan Bội Châu tại Huế là nơi cụ đã sống những năm tháng cuối đời (1925-1940), gắn liền với biệt danh 'Ông già Bến Ngự'. Nơi đây lưu giữ nhiều kỷ vật và là di tích lịch sử văn hóa cấp quốc gia.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4039,22 +4051,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
@@ -4475,17 +4487,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>user_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>location_name</t>
         </is>
